--- a/results/excel/result3.xlsx
+++ b/results/excel/result3.xlsx
@@ -466,69 +466,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C2" t="n">
-        <v>9628223555</v>
+        <v>4190988310</v>
       </c>
       <c r="D2" t="n">
-        <v>1465</v>
+        <v>3501</v>
       </c>
       <c r="E2" t="n">
-        <v>300.1</v>
+        <v>29.36</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>1173</v>
+        <v>54</v>
       </c>
       <c r="I2" t="n">
-        <v>222</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>500635396</v>
       </c>
       <c r="C3" t="n">
-        <v>9700005700</v>
+        <v>9657930100</v>
       </c>
       <c r="D3" t="n">
-        <v>5248</v>
+        <v>5874</v>
       </c>
       <c r="E3" t="n">
-        <v>17.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>1208</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>4430</v>
       </c>
       <c r="H3" t="n">
-        <v>88</v>
+        <v>12980</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -553,38 +553,38 @@
         <v>2640</v>
       </c>
       <c r="I4" t="n">
-        <v>265</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>63563817</v>
       </c>
       <c r="C5" t="n">
-        <v>1841014603</v>
+        <v>2874903000</v>
       </c>
       <c r="D5" t="n">
-        <v>3304</v>
+        <v>4667</v>
       </c>
       <c r="E5" t="n">
-        <v>38.14</v>
+        <v>28.63</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="I5" t="n">
-        <v>326</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -594,183 +594,183 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C6" t="n">
-        <v>1841014603</v>
+        <v>9630806627</v>
       </c>
       <c r="D6" t="n">
-        <v>3169</v>
+        <v>1242</v>
       </c>
       <c r="E6" t="n">
-        <v>38.14</v>
+        <v>358.77</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>382</v>
       </c>
       <c r="H6" t="n">
-        <v>106</v>
+        <v>1119</v>
       </c>
       <c r="I6" t="n">
-        <v>326</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C7" t="n">
-        <v>8878077181</v>
+        <v>4190988310</v>
       </c>
       <c r="D7" t="n">
-        <v>1048</v>
+        <v>2980</v>
       </c>
       <c r="E7" t="n">
-        <v>539.88</v>
+        <v>29.36</v>
       </c>
       <c r="F7" t="n">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>901</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>2640</v>
+        <v>54</v>
       </c>
       <c r="I7" t="n">
-        <v>265</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>63563817</v>
       </c>
       <c r="C8" t="n">
-        <v>4190988310</v>
+        <v>4190988309</v>
       </c>
       <c r="D8" t="n">
-        <v>5812</v>
+        <v>6224</v>
       </c>
       <c r="E8" t="n">
-        <v>29.36</v>
+        <v>30.55</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I8" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C9" t="n">
-        <v>4190988310</v>
+        <v>9773660250</v>
       </c>
       <c r="D9" t="n">
-        <v>1108</v>
+        <v>4514</v>
       </c>
       <c r="E9" t="n">
-        <v>29.36</v>
+        <v>264.52</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H9" t="n">
-        <v>54</v>
+        <v>281</v>
       </c>
       <c r="I9" t="n">
-        <v>234</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C10" t="n">
-        <v>4190988310</v>
+        <v>9773660250</v>
       </c>
       <c r="D10" t="n">
-        <v>1108</v>
+        <v>4514</v>
       </c>
       <c r="E10" t="n">
-        <v>29.36</v>
+        <v>264.52</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H10" t="n">
-        <v>54</v>
+        <v>281</v>
       </c>
       <c r="I10" t="n">
-        <v>234</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C11" t="n">
-        <v>9773660250</v>
+        <v>4190988309</v>
       </c>
       <c r="D11" t="n">
-        <v>4514</v>
+        <v>3617</v>
       </c>
       <c r="E11" t="n">
-        <v>264.52</v>
+        <v>30.55</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="I11" t="n">
-        <v>1560</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -783,62 +783,62 @@
         <v>63563817</v>
       </c>
       <c r="C12" t="n">
-        <v>4190988310</v>
+        <v>2874903000</v>
       </c>
       <c r="D12" t="n">
-        <v>2212</v>
+        <v>1490</v>
       </c>
       <c r="E12" t="n">
-        <v>29.36</v>
+        <v>28.63</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H12" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I12" t="n">
-        <v>234</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C13" t="n">
-        <v>9657930100</v>
+        <v>9628223555</v>
       </c>
       <c r="D13" t="n">
-        <v>5874</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>4474.67</v>
+        <v>300.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1208</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>4430</v>
+        <v>400</v>
       </c>
       <c r="H13" t="n">
-        <v>12980</v>
+        <v>1173</v>
       </c>
       <c r="I13" t="n">
-        <v>388</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -848,7 +848,7 @@
         <v>4190988309</v>
       </c>
       <c r="D14" t="n">
-        <v>6245</v>
+        <v>6082</v>
       </c>
       <c r="E14" t="n">
         <v>30.55</v>
@@ -863,193 +863,193 @@
         <v>57</v>
       </c>
       <c r="I14" t="n">
-        <v>502</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>495817671</v>
+        <v>500635396</v>
       </c>
       <c r="C15" t="n">
-        <v>9630806627</v>
+        <v>9700005700</v>
       </c>
       <c r="D15" t="n">
-        <v>3104</v>
+        <v>5453</v>
       </c>
       <c r="E15" t="n">
-        <v>358.77</v>
+        <v>17.63</v>
       </c>
       <c r="F15" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>382</v>
+        <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>1119</v>
+        <v>88</v>
       </c>
       <c r="I15" t="n">
-        <v>156</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C16" t="n">
-        <v>2874903000</v>
+        <v>8878077181</v>
       </c>
       <c r="D16" t="n">
-        <v>5351</v>
+        <v>3989</v>
       </c>
       <c r="E16" t="n">
-        <v>28.63</v>
+        <v>539.88</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>901</v>
       </c>
       <c r="H16" t="n">
-        <v>83</v>
+        <v>2640</v>
       </c>
       <c r="I16" t="n">
-        <v>409</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C17" t="n">
-        <v>9657930100</v>
+        <v>4190988310</v>
       </c>
       <c r="D17" t="n">
-        <v>5874</v>
+        <v>228</v>
       </c>
       <c r="E17" t="n">
-        <v>4474.67</v>
+        <v>29.36</v>
       </c>
       <c r="F17" t="n">
-        <v>1208</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>4430</v>
+        <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>12980</v>
+        <v>54</v>
       </c>
       <c r="I17" t="n">
-        <v>388</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C18" t="n">
-        <v>8878077181</v>
+        <v>9657930100</v>
       </c>
       <c r="D18" t="n">
-        <v>1048</v>
+        <v>5573</v>
       </c>
       <c r="E18" t="n">
-        <v>539.88</v>
+        <v>4474.67</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>1208</v>
       </c>
       <c r="G18" t="n">
-        <v>901</v>
+        <v>4430</v>
       </c>
       <c r="H18" t="n">
-        <v>2640</v>
+        <v>12980</v>
       </c>
       <c r="I18" t="n">
-        <v>265</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C19" t="n">
-        <v>9700005700</v>
+        <v>4190988309</v>
       </c>
       <c r="D19" t="n">
-        <v>6656</v>
+        <v>6245</v>
       </c>
       <c r="E19" t="n">
-        <v>17.63</v>
+        <v>30.55</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H19" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C20" t="n">
-        <v>2874903000</v>
+        <v>9811363528</v>
       </c>
       <c r="D20" t="n">
-        <v>5995</v>
+        <v>3179</v>
       </c>
       <c r="E20" t="n">
-        <v>28.63</v>
+        <v>311.78</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>28</v>
+        <v>433</v>
       </c>
       <c r="H20" t="n">
-        <v>83</v>
+        <v>1268</v>
       </c>
       <c r="I20" t="n">
-        <v>409</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -1059,344 +1059,344 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C21" t="n">
-        <v>9700005700</v>
+        <v>1841014603</v>
       </c>
       <c r="D21" t="n">
-        <v>5963</v>
+        <v>5267</v>
       </c>
       <c r="E21" t="n">
-        <v>17.63</v>
+        <v>38.14</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H21" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C22" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D22" t="n">
-        <v>154</v>
+        <v>5061</v>
       </c>
       <c r="E22" t="n">
-        <v>300.1</v>
+        <v>358.77</v>
       </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="G22" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="H22" t="n">
-        <v>1173</v>
+        <v>1119</v>
       </c>
       <c r="I22" t="n">
-        <v>222</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C23" t="n">
-        <v>9628223555</v>
+        <v>9657930100</v>
       </c>
       <c r="D23" t="n">
-        <v>652</v>
+        <v>998</v>
       </c>
       <c r="E23" t="n">
-        <v>300.1</v>
+        <v>4474.67</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>1208</v>
       </c>
       <c r="G23" t="n">
-        <v>400</v>
+        <v>4430</v>
       </c>
       <c r="H23" t="n">
-        <v>1173</v>
+        <v>12980</v>
       </c>
       <c r="I23" t="n">
-        <v>222</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C24" t="n">
-        <v>9811363528</v>
+        <v>2874903000</v>
       </c>
       <c r="D24" t="n">
-        <v>4255</v>
+        <v>2499</v>
       </c>
       <c r="E24" t="n">
-        <v>311.78</v>
+        <v>28.63</v>
       </c>
       <c r="F24" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="H24" t="n">
-        <v>1268</v>
+        <v>83</v>
       </c>
       <c r="I24" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C25" t="n">
-        <v>9700005700</v>
+        <v>4190988310</v>
       </c>
       <c r="D25" t="n">
-        <v>5963</v>
+        <v>5840</v>
       </c>
       <c r="E25" t="n">
-        <v>17.63</v>
+        <v>29.36</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H25" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C26" t="n">
-        <v>1841014603</v>
+        <v>9700005700</v>
       </c>
       <c r="D26" t="n">
-        <v>2889</v>
+        <v>5963</v>
       </c>
       <c r="E26" t="n">
-        <v>38.14</v>
+        <v>17.63</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="I26" t="n">
-        <v>326</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C27" t="n">
-        <v>9628223555</v>
+        <v>4190988310</v>
       </c>
       <c r="D27" t="n">
-        <v>1647</v>
+        <v>1583</v>
       </c>
       <c r="E27" t="n">
-        <v>300.1</v>
+        <v>29.36</v>
       </c>
       <c r="F27" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>1173</v>
+        <v>54</v>
       </c>
       <c r="I27" t="n">
-        <v>222</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C28" t="n">
-        <v>9700005700</v>
+        <v>9628223555</v>
       </c>
       <c r="D28" t="n">
-        <v>4956</v>
+        <v>1285</v>
       </c>
       <c r="E28" t="n">
-        <v>17.63</v>
+        <v>300.1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="H28" t="n">
-        <v>88</v>
+        <v>1173</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C29" t="n">
-        <v>2874903000</v>
+        <v>9700005700</v>
       </c>
       <c r="D29" t="n">
-        <v>193</v>
+        <v>5453</v>
       </c>
       <c r="E29" t="n">
-        <v>28.63</v>
+        <v>17.63</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H29" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I29" t="n">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C30" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D30" t="n">
-        <v>5655</v>
+        <v>5928</v>
       </c>
       <c r="E30" t="n">
-        <v>358.77</v>
+        <v>311.78</v>
       </c>
       <c r="F30" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="H30" t="n">
-        <v>1119</v>
+        <v>1268</v>
       </c>
       <c r="I30" t="n">
-        <v>156</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>63563817</v>
       </c>
       <c r="C31" t="n">
-        <v>4190988310</v>
+        <v>2874903000</v>
       </c>
       <c r="D31" t="n">
-        <v>4713</v>
+        <v>4738</v>
       </c>
       <c r="E31" t="n">
-        <v>29.36</v>
+        <v>28.63</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H31" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I31" t="n">
-        <v>234</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1406,7 +1406,7 @@
         <v>1841014603</v>
       </c>
       <c r="D32" t="n">
-        <v>3169</v>
+        <v>4675</v>
       </c>
       <c r="E32" t="n">
         <v>38.14</v>
@@ -1421,106 +1421,106 @@
         <v>106</v>
       </c>
       <c r="I32" t="n">
-        <v>326</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>495817671</v>
+        <v>500635396</v>
       </c>
       <c r="C33" t="n">
-        <v>9630806627</v>
+        <v>9700005700</v>
       </c>
       <c r="D33" t="n">
-        <v>5050</v>
+        <v>6656</v>
       </c>
       <c r="E33" t="n">
-        <v>358.77</v>
+        <v>17.63</v>
       </c>
       <c r="F33" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>382</v>
+        <v>30</v>
       </c>
       <c r="H33" t="n">
-        <v>1119</v>
+        <v>88</v>
       </c>
       <c r="I33" t="n">
-        <v>156</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C34" t="n">
-        <v>2526158329</v>
+        <v>9657930100</v>
       </c>
       <c r="D34" t="n">
-        <v>5700</v>
+        <v>6133</v>
       </c>
       <c r="E34" t="n">
-        <v>12.66</v>
+        <v>4474.67</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1208</v>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>4430</v>
       </c>
       <c r="H34" t="n">
-        <v>24</v>
+        <v>12980</v>
       </c>
       <c r="I34" t="n">
-        <v>3451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C35" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D35" t="n">
-        <v>1048</v>
+        <v>4514</v>
       </c>
       <c r="E35" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F35" t="n">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="G35" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H35" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I35" t="n">
-        <v>265</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1530,7 +1530,7 @@
         <v>8878077181</v>
       </c>
       <c r="D36" t="n">
-        <v>1048</v>
+        <v>3989</v>
       </c>
       <c r="E36" t="n">
         <v>539.88</v>
@@ -1545,44 +1545,44 @@
         <v>2640</v>
       </c>
       <c r="I36" t="n">
-        <v>265</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C37" t="n">
-        <v>8878077181</v>
+        <v>9657930100</v>
       </c>
       <c r="D37" t="n">
-        <v>3989</v>
+        <v>998</v>
       </c>
       <c r="E37" t="n">
-        <v>539.88</v>
+        <v>4474.67</v>
       </c>
       <c r="F37" t="n">
-        <v>146</v>
+        <v>1208</v>
       </c>
       <c r="G37" t="n">
-        <v>901</v>
+        <v>4430</v>
       </c>
       <c r="H37" t="n">
-        <v>2640</v>
+        <v>12980</v>
       </c>
       <c r="I37" t="n">
-        <v>265</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1592,7 +1592,7 @@
         <v>9657930100</v>
       </c>
       <c r="D38" t="n">
-        <v>5573</v>
+        <v>998</v>
       </c>
       <c r="E38" t="n">
         <v>4474.67</v>
@@ -1607,44 +1607,44 @@
         <v>12980</v>
       </c>
       <c r="I38" t="n">
-        <v>388</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C39" t="n">
-        <v>9773660250</v>
+        <v>9628223555</v>
       </c>
       <c r="D39" t="n">
-        <v>4514</v>
+        <v>4865</v>
       </c>
       <c r="E39" t="n">
-        <v>264.52</v>
+        <v>300.1</v>
       </c>
       <c r="F39" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G39" t="n">
-        <v>96</v>
+        <v>400</v>
       </c>
       <c r="H39" t="n">
-        <v>281</v>
+        <v>1173</v>
       </c>
       <c r="I39" t="n">
-        <v>1560</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1654,7 +1654,7 @@
         <v>9657930100</v>
       </c>
       <c r="D40" t="n">
-        <v>3587</v>
+        <v>5874</v>
       </c>
       <c r="E40" t="n">
         <v>4474.67</v>
@@ -1669,224 +1669,224 @@
         <v>12980</v>
       </c>
       <c r="I40" t="n">
-        <v>388</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C41" t="n">
-        <v>9811363528</v>
+        <v>2874903000</v>
       </c>
       <c r="D41" t="n">
-        <v>1688</v>
+        <v>2596</v>
       </c>
       <c r="E41" t="n">
-        <v>311.78</v>
+        <v>28.63</v>
       </c>
       <c r="F41" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="H41" t="n">
-        <v>1268</v>
+        <v>83</v>
       </c>
       <c r="I41" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C42" t="n">
-        <v>9773660250</v>
+        <v>1841014603</v>
       </c>
       <c r="D42" t="n">
-        <v>4514</v>
+        <v>3304</v>
       </c>
       <c r="E42" t="n">
-        <v>264.52</v>
+        <v>38.14</v>
       </c>
       <c r="F42" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="H42" t="n">
-        <v>281</v>
+        <v>106</v>
       </c>
       <c r="I42" t="n">
-        <v>1560</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C43" t="n">
-        <v>9811363528</v>
+        <v>9700005700</v>
       </c>
       <c r="D43" t="n">
-        <v>5596</v>
+        <v>5248</v>
       </c>
       <c r="E43" t="n">
-        <v>311.78</v>
+        <v>17.63</v>
       </c>
       <c r="F43" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>433</v>
+        <v>30</v>
       </c>
       <c r="H43" t="n">
-        <v>1268</v>
+        <v>88</v>
       </c>
       <c r="I43" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>500635396</v>
       </c>
       <c r="C44" t="n">
-        <v>9657930100</v>
+        <v>9773660250</v>
       </c>
       <c r="D44" t="n">
-        <v>998</v>
+        <v>4514</v>
       </c>
       <c r="E44" t="n">
-        <v>4474.67</v>
+        <v>264.52</v>
       </c>
       <c r="F44" t="n">
-        <v>1208</v>
+        <v>71</v>
       </c>
       <c r="G44" t="n">
-        <v>4430</v>
+        <v>96</v>
       </c>
       <c r="H44" t="n">
-        <v>12980</v>
+        <v>281</v>
       </c>
       <c r="I44" t="n">
-        <v>388</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C45" t="n">
-        <v>1841014603</v>
+        <v>9811363528</v>
       </c>
       <c r="D45" t="n">
-        <v>5267</v>
+        <v>3716</v>
       </c>
       <c r="E45" t="n">
-        <v>38.14</v>
+        <v>311.78</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="G45" t="n">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="H45" t="n">
-        <v>106</v>
+        <v>1268</v>
       </c>
       <c r="I45" t="n">
-        <v>326</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C46" t="n">
-        <v>2874903000</v>
+        <v>9657930100</v>
       </c>
       <c r="D46" t="n">
-        <v>2596</v>
+        <v>3587</v>
       </c>
       <c r="E46" t="n">
-        <v>28.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>1208</v>
       </c>
       <c r="G46" t="n">
-        <v>28</v>
+        <v>4430</v>
       </c>
       <c r="H46" t="n">
-        <v>83</v>
+        <v>12980</v>
       </c>
       <c r="I46" t="n">
-        <v>409</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>500635396</v>
       </c>
       <c r="C47" t="n">
-        <v>9657930100</v>
+        <v>9773660250</v>
       </c>
       <c r="D47" t="n">
-        <v>3587</v>
+        <v>4514</v>
       </c>
       <c r="E47" t="n">
-        <v>4474.67</v>
+        <v>264.52</v>
       </c>
       <c r="F47" t="n">
-        <v>1208</v>
+        <v>71</v>
       </c>
       <c r="G47" t="n">
-        <v>4430</v>
+        <v>96</v>
       </c>
       <c r="H47" t="n">
-        <v>12980</v>
+        <v>281</v>
       </c>
       <c r="I47" t="n">
-        <v>388</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -1896,34 +1896,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C48" t="n">
-        <v>9700005700</v>
+        <v>2526158329</v>
       </c>
       <c r="D48" t="n">
-        <v>4956</v>
+        <v>3286</v>
       </c>
       <c r="E48" t="n">
-        <v>17.63</v>
+        <v>12.66</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H48" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1933,7 +1933,7 @@
         <v>2874903000</v>
       </c>
       <c r="D49" t="n">
-        <v>5241</v>
+        <v>2574</v>
       </c>
       <c r="E49" t="n">
         <v>28.63</v>
@@ -1948,44 +1948,44 @@
         <v>83</v>
       </c>
       <c r="I49" t="n">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C50" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D50" t="n">
-        <v>5755</v>
+        <v>6224</v>
       </c>
       <c r="E50" t="n">
-        <v>311.78</v>
+        <v>30.55</v>
       </c>
       <c r="F50" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="H50" t="n">
-        <v>1268</v>
+        <v>57</v>
       </c>
       <c r="I50" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1995,7 +1995,7 @@
         <v>9811363528</v>
       </c>
       <c r="D51" t="n">
-        <v>2116</v>
+        <v>4639</v>
       </c>
       <c r="E51" t="n">
         <v>311.78</v>
@@ -2010,193 +2010,193 @@
         <v>1268</v>
       </c>
       <c r="I51" t="n">
-        <v>119</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C52" t="n">
-        <v>9773660250</v>
+        <v>4190988310</v>
       </c>
       <c r="D52" t="n">
-        <v>4514</v>
+        <v>2294</v>
       </c>
       <c r="E52" t="n">
-        <v>264.52</v>
+        <v>29.36</v>
       </c>
       <c r="F52" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="H52" t="n">
-        <v>281</v>
+        <v>54</v>
       </c>
       <c r="I52" t="n">
-        <v>1560</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C53" t="n">
-        <v>8878077181</v>
+        <v>2874903000</v>
       </c>
       <c r="D53" t="n">
-        <v>3989</v>
+        <v>648</v>
       </c>
       <c r="E53" t="n">
-        <v>539.88</v>
+        <v>28.63</v>
       </c>
       <c r="F53" t="n">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>901</v>
+        <v>28</v>
       </c>
       <c r="H53" t="n">
-        <v>2640</v>
+        <v>83</v>
       </c>
       <c r="I53" t="n">
-        <v>265</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C54" t="n">
-        <v>9700005700</v>
+        <v>9811363528</v>
       </c>
       <c r="D54" t="n">
-        <v>4956</v>
+        <v>3043</v>
       </c>
       <c r="E54" t="n">
-        <v>17.63</v>
+        <v>311.78</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="G54" t="n">
-        <v>30</v>
+        <v>433</v>
       </c>
       <c r="H54" t="n">
-        <v>88</v>
+        <v>1268</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>495403620</v>
       </c>
       <c r="C55" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D55" t="n">
-        <v>4388</v>
+        <v>3989</v>
       </c>
       <c r="E55" t="n">
-        <v>300.1</v>
+        <v>539.88</v>
       </c>
       <c r="F55" t="n">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="G55" t="n">
-        <v>400</v>
+        <v>901</v>
       </c>
       <c r="H55" t="n">
-        <v>1173</v>
+        <v>2640</v>
       </c>
       <c r="I55" t="n">
-        <v>222</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C56" t="n">
-        <v>4190988309</v>
+        <v>9773660250</v>
       </c>
       <c r="D56" t="n">
-        <v>6082</v>
+        <v>4514</v>
       </c>
       <c r="E56" t="n">
-        <v>30.55</v>
+        <v>264.52</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="G56" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H56" t="n">
-        <v>57</v>
+        <v>281</v>
       </c>
       <c r="I56" t="n">
-        <v>502</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C57" t="n">
-        <v>9657930100</v>
+        <v>9630806627</v>
       </c>
       <c r="D57" t="n">
-        <v>998</v>
+        <v>4016</v>
       </c>
       <c r="E57" t="n">
-        <v>4474.67</v>
+        <v>358.77</v>
       </c>
       <c r="F57" t="n">
-        <v>1208</v>
+        <v>97</v>
       </c>
       <c r="G57" t="n">
-        <v>4430</v>
+        <v>382</v>
       </c>
       <c r="H57" t="n">
-        <v>12980</v>
+        <v>1119</v>
       </c>
       <c r="I57" t="n">
-        <v>388</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
@@ -2206,214 +2206,214 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C58" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D58" t="n">
-        <v>2859</v>
+        <v>1048</v>
       </c>
       <c r="E58" t="n">
-        <v>311.78</v>
+        <v>539.88</v>
       </c>
       <c r="F58" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="G58" t="n">
-        <v>433</v>
+        <v>901</v>
       </c>
       <c r="H58" t="n">
-        <v>1268</v>
+        <v>2640</v>
       </c>
       <c r="I58" t="n">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C59" t="n">
-        <v>2874903000</v>
+        <v>8878077181</v>
       </c>
       <c r="D59" t="n">
-        <v>2499</v>
+        <v>3989</v>
       </c>
       <c r="E59" t="n">
-        <v>28.63</v>
+        <v>539.88</v>
       </c>
       <c r="F59" t="n">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="G59" t="n">
-        <v>28</v>
+        <v>901</v>
       </c>
       <c r="H59" t="n">
-        <v>83</v>
+        <v>2640</v>
       </c>
       <c r="I59" t="n">
-        <v>409</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C60" t="n">
-        <v>1841014603</v>
+        <v>9630806627</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>4606</v>
       </c>
       <c r="E60" t="n">
-        <v>38.14</v>
+        <v>358.77</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="G60" t="n">
-        <v>36</v>
+        <v>382</v>
       </c>
       <c r="H60" t="n">
-        <v>106</v>
+        <v>1119</v>
       </c>
       <c r="I60" t="n">
-        <v>326</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C61" t="n">
-        <v>2874903000</v>
+        <v>8878077181</v>
       </c>
       <c r="D61" t="n">
-        <v>2499</v>
+        <v>1048</v>
       </c>
       <c r="E61" t="n">
-        <v>28.63</v>
+        <v>539.88</v>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="G61" t="n">
-        <v>28</v>
+        <v>901</v>
       </c>
       <c r="H61" t="n">
-        <v>83</v>
+        <v>2640</v>
       </c>
       <c r="I61" t="n">
-        <v>409</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C62" t="n">
-        <v>9630806627</v>
+        <v>4190988310</v>
       </c>
       <c r="D62" t="n">
-        <v>2997</v>
+        <v>3818</v>
       </c>
       <c r="E62" t="n">
-        <v>358.77</v>
+        <v>29.36</v>
       </c>
       <c r="F62" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="H62" t="n">
-        <v>1119</v>
+        <v>54</v>
       </c>
       <c r="I62" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>63563817</v>
       </c>
       <c r="C63" t="n">
-        <v>4190988309</v>
+        <v>1841014603</v>
       </c>
       <c r="D63" t="n">
-        <v>6245</v>
+        <v>2889</v>
       </c>
       <c r="E63" t="n">
-        <v>30.55</v>
+        <v>38.14</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G63" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H63" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="I63" t="n">
-        <v>502</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>63563817</v>
       </c>
       <c r="C64" t="n">
-        <v>4190988309</v>
+        <v>4190988310</v>
       </c>
       <c r="D64" t="n">
-        <v>6224</v>
+        <v>3501</v>
       </c>
       <c r="E64" t="n">
-        <v>30.55</v>
+        <v>29.36</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H64" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I64" t="n">
-        <v>502</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2423,121 +2423,121 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C65" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>5862</v>
       </c>
       <c r="E65" t="n">
-        <v>38.14</v>
+        <v>300.1</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="G65" t="n">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="H65" t="n">
-        <v>106</v>
+        <v>1173</v>
       </c>
       <c r="I65" t="n">
-        <v>326</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C66" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D66" t="n">
-        <v>2097</v>
+        <v>2889</v>
       </c>
       <c r="E66" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F66" t="n">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H66" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I66" t="n">
-        <v>156</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C67" t="n">
-        <v>9773660250</v>
+        <v>9811363528</v>
       </c>
       <c r="D67" t="n">
-        <v>4514</v>
+        <v>2655</v>
       </c>
       <c r="E67" t="n">
-        <v>264.52</v>
+        <v>311.78</v>
       </c>
       <c r="F67" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G67" t="n">
-        <v>96</v>
+        <v>433</v>
       </c>
       <c r="H67" t="n">
-        <v>281</v>
+        <v>1268</v>
       </c>
       <c r="I67" t="n">
-        <v>1560</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C68" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D68" t="n">
-        <v>2706</v>
+        <v>5273</v>
       </c>
       <c r="E68" t="n">
-        <v>30.55</v>
+        <v>358.77</v>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="G68" t="n">
-        <v>19</v>
+        <v>382</v>
       </c>
       <c r="H68" t="n">
-        <v>57</v>
+        <v>1119</v>
       </c>
       <c r="I68" t="n">
-        <v>502</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69">
@@ -2550,397 +2550,397 @@
         <v>63563817</v>
       </c>
       <c r="C69" t="n">
-        <v>1841014603</v>
+        <v>2874903000</v>
       </c>
       <c r="D69" t="n">
-        <v>4186</v>
+        <v>2574</v>
       </c>
       <c r="E69" t="n">
-        <v>38.14</v>
+        <v>28.63</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H69" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="I69" t="n">
-        <v>326</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C70" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D70" t="n">
-        <v>2206</v>
+        <v>1853</v>
       </c>
       <c r="E70" t="n">
-        <v>311.78</v>
+        <v>358.77</v>
       </c>
       <c r="F70" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G70" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H70" t="n">
-        <v>1268</v>
+        <v>1119</v>
       </c>
       <c r="I70" t="n">
-        <v>119</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C71" t="n">
-        <v>4190988309</v>
+        <v>9773660250</v>
       </c>
       <c r="D71" t="n">
-        <v>2397</v>
+        <v>4514</v>
       </c>
       <c r="E71" t="n">
-        <v>30.55</v>
+        <v>264.52</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="G71" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H71" t="n">
-        <v>57</v>
+        <v>281</v>
       </c>
       <c r="I71" t="n">
-        <v>502</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C72" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D72" t="n">
-        <v>530</v>
+        <v>6245</v>
       </c>
       <c r="E72" t="n">
-        <v>358.77</v>
+        <v>30.55</v>
       </c>
       <c r="F72" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="H72" t="n">
-        <v>1119</v>
+        <v>57</v>
       </c>
       <c r="I72" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C73" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D73" t="n">
-        <v>6224</v>
+        <v>2093</v>
       </c>
       <c r="E73" t="n">
-        <v>30.55</v>
+        <v>300.1</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="G73" t="n">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="H73" t="n">
-        <v>57</v>
+        <v>1173</v>
       </c>
       <c r="I73" t="n">
-        <v>502</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C74" t="n">
-        <v>4190988309</v>
+        <v>9700005700</v>
       </c>
       <c r="D74" t="n">
-        <v>6224</v>
+        <v>4956</v>
       </c>
       <c r="E74" t="n">
-        <v>30.55</v>
+        <v>17.63</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H74" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="I74" t="n">
-        <v>502</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C75" t="n">
-        <v>9811363528</v>
+        <v>9700005700</v>
       </c>
       <c r="D75" t="n">
-        <v>5013</v>
+        <v>1900</v>
       </c>
       <c r="E75" t="n">
-        <v>311.78</v>
+        <v>17.63</v>
       </c>
       <c r="F75" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>433</v>
+        <v>30</v>
       </c>
       <c r="H75" t="n">
-        <v>1268</v>
+        <v>88</v>
       </c>
       <c r="I75" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C76" t="n">
-        <v>9700005700</v>
+        <v>9811363528</v>
       </c>
       <c r="D76" t="n">
-        <v>5963</v>
+        <v>3692</v>
       </c>
       <c r="E76" t="n">
-        <v>17.63</v>
+        <v>311.78</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="G76" t="n">
-        <v>30</v>
+        <v>433</v>
       </c>
       <c r="H76" t="n">
-        <v>88</v>
+        <v>1268</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C77" t="n">
-        <v>9773660250</v>
+        <v>9628223555</v>
       </c>
       <c r="D77" t="n">
-        <v>4514</v>
+        <v>1719</v>
       </c>
       <c r="E77" t="n">
-        <v>264.52</v>
+        <v>300.1</v>
       </c>
       <c r="F77" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G77" t="n">
-        <v>96</v>
+        <v>400</v>
       </c>
       <c r="H77" t="n">
-        <v>281</v>
+        <v>1173</v>
       </c>
       <c r="I77" t="n">
-        <v>1560</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C78" t="n">
-        <v>4190988310</v>
+        <v>9811363528</v>
       </c>
       <c r="D78" t="n">
-        <v>4155</v>
+        <v>6130</v>
       </c>
       <c r="E78" t="n">
-        <v>29.36</v>
+        <v>311.78</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="G78" t="n">
-        <v>18</v>
+        <v>433</v>
       </c>
       <c r="H78" t="n">
-        <v>54</v>
+        <v>1268</v>
       </c>
       <c r="I78" t="n">
-        <v>234</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C79" t="n">
-        <v>4190988310</v>
+        <v>9628223555</v>
       </c>
       <c r="D79" t="n">
-        <v>4155</v>
+        <v>1465</v>
       </c>
       <c r="E79" t="n">
-        <v>29.36</v>
+        <v>300.1</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="G79" t="n">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="H79" t="n">
-        <v>54</v>
+        <v>1173</v>
       </c>
       <c r="I79" t="n">
-        <v>234</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>500635396</v>
       </c>
       <c r="C80" t="n">
-        <v>9773660250</v>
+        <v>9700005700</v>
       </c>
       <c r="D80" t="n">
-        <v>4514</v>
+        <v>5963</v>
       </c>
       <c r="E80" t="n">
-        <v>264.52</v>
+        <v>17.63</v>
       </c>
       <c r="F80" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="H80" t="n">
-        <v>281</v>
+        <v>88</v>
       </c>
       <c r="I80" t="n">
-        <v>1560</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C81" t="n">
-        <v>9628223555</v>
+        <v>4190988309</v>
       </c>
       <c r="D81" t="n">
-        <v>14</v>
+        <v>3617</v>
       </c>
       <c r="E81" t="n">
-        <v>300.1</v>
+        <v>30.55</v>
       </c>
       <c r="F81" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="H81" t="n">
-        <v>1173</v>
+        <v>57</v>
       </c>
       <c r="I81" t="n">
-        <v>222</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2950,220 +2950,220 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C82" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D82" t="n">
-        <v>4467</v>
+        <v>4186</v>
       </c>
       <c r="E82" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F82" t="n">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H82" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I82" t="n">
-        <v>156</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C83" t="n">
-        <v>9628223555</v>
+        <v>1841014603</v>
       </c>
       <c r="D83" t="n">
-        <v>6440</v>
+        <v>4713</v>
       </c>
       <c r="E83" t="n">
-        <v>300.1</v>
+        <v>38.14</v>
       </c>
       <c r="F83" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="G83" t="n">
-        <v>400</v>
+        <v>36</v>
       </c>
       <c r="H83" t="n">
-        <v>1173</v>
+        <v>106</v>
       </c>
       <c r="I83" t="n">
-        <v>222</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C84" t="n">
-        <v>9773660250</v>
+        <v>9630806627</v>
       </c>
       <c r="D84" t="n">
-        <v>4514</v>
+        <v>3913</v>
       </c>
       <c r="E84" t="n">
-        <v>264.52</v>
+        <v>358.77</v>
       </c>
       <c r="F84" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="G84" t="n">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="H84" t="n">
-        <v>281</v>
+        <v>1119</v>
       </c>
       <c r="I84" t="n">
-        <v>1560</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C85" t="n">
-        <v>9657930100</v>
+        <v>8878077181</v>
       </c>
       <c r="D85" t="n">
-        <v>6133</v>
+        <v>3989</v>
       </c>
       <c r="E85" t="n">
-        <v>4474.67</v>
+        <v>539.88</v>
       </c>
       <c r="F85" t="n">
-        <v>1208</v>
+        <v>146</v>
       </c>
       <c r="G85" t="n">
-        <v>4430</v>
+        <v>901</v>
       </c>
       <c r="H85" t="n">
-        <v>12980</v>
+        <v>2640</v>
       </c>
       <c r="I85" t="n">
-        <v>388</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C86" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D86" t="n">
-        <v>2152</v>
+        <v>5267</v>
       </c>
       <c r="E86" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F86" t="n">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I86" t="n">
-        <v>156</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C87" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D87" t="n">
-        <v>1048</v>
+        <v>4514</v>
       </c>
       <c r="E87" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F87" t="n">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="G87" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H87" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I87" t="n">
-        <v>265</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C88" t="n">
-        <v>2874903000</v>
+        <v>9630806627</v>
       </c>
       <c r="D88" t="n">
-        <v>4836</v>
+        <v>292</v>
       </c>
       <c r="E88" t="n">
-        <v>28.63</v>
+        <v>358.77</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="G88" t="n">
-        <v>28</v>
+        <v>382</v>
       </c>
       <c r="H88" t="n">
-        <v>83</v>
+        <v>1119</v>
       </c>
       <c r="I88" t="n">
-        <v>409</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3173,7 +3173,7 @@
         <v>9628223555</v>
       </c>
       <c r="D89" t="n">
-        <v>1094</v>
+        <v>6210</v>
       </c>
       <c r="E89" t="n">
         <v>300.1</v>
@@ -3188,38 +3188,38 @@
         <v>1173</v>
       </c>
       <c r="I89" t="n">
-        <v>222</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>63563817</v>
       </c>
       <c r="C90" t="n">
-        <v>4190988310</v>
+        <v>4190988309</v>
       </c>
       <c r="D90" t="n">
-        <v>5812</v>
+        <v>6082</v>
       </c>
       <c r="E90" t="n">
-        <v>29.36</v>
+        <v>30.55</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H90" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I90" t="n">
-        <v>234</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result3.xlsx
+++ b/results/excel/result3.xlsx
@@ -466,38 +466,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C2" t="n">
-        <v>4190988310</v>
+        <v>8878077181</v>
       </c>
       <c r="D2" t="n">
-        <v>3501</v>
+        <v>1048</v>
       </c>
       <c r="E2" t="n">
-        <v>29.36</v>
+        <v>539.88</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>1054</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>901</v>
       </c>
       <c r="H2" t="n">
-        <v>54</v>
+        <v>2640</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -507,13 +507,13 @@
         <v>9657930100</v>
       </c>
       <c r="D3" t="n">
-        <v>5874</v>
+        <v>998</v>
       </c>
       <c r="E3" t="n">
         <v>4474.67</v>
       </c>
       <c r="F3" t="n">
-        <v>1208</v>
+        <v>25139</v>
       </c>
       <c r="G3" t="n">
         <v>4430</v>
@@ -522,7 +522,7 @@
         <v>12980</v>
       </c>
       <c r="I3" t="n">
-        <v>453</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4">
@@ -532,34 +532,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C4" t="n">
-        <v>8878077181</v>
+        <v>9628223555</v>
       </c>
       <c r="D4" t="n">
-        <v>1048</v>
+        <v>6542</v>
       </c>
       <c r="E4" t="n">
-        <v>539.88</v>
+        <v>300.1</v>
       </c>
       <c r="F4" t="n">
-        <v>146</v>
+        <v>2619</v>
       </c>
       <c r="G4" t="n">
-        <v>901</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>2640</v>
+        <v>1173</v>
       </c>
       <c r="I4" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -569,13 +569,13 @@
         <v>2874903000</v>
       </c>
       <c r="D5" t="n">
-        <v>4667</v>
+        <v>2959</v>
       </c>
       <c r="E5" t="n">
         <v>28.63</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="G5" t="n">
         <v>28</v>
@@ -584,97 +584,97 @@
         <v>83</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C6" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D6" t="n">
-        <v>1242</v>
+        <v>3989</v>
       </c>
       <c r="E6" t="n">
-        <v>358.77</v>
+        <v>539.88</v>
       </c>
       <c r="F6" t="n">
-        <v>97</v>
+        <v>1054</v>
       </c>
       <c r="G6" t="n">
-        <v>382</v>
+        <v>901</v>
       </c>
       <c r="H6" t="n">
-        <v>1119</v>
+        <v>2640</v>
       </c>
       <c r="I6" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C7" t="n">
-        <v>4190988310</v>
+        <v>9773660250</v>
       </c>
       <c r="D7" t="n">
-        <v>2980</v>
+        <v>4514</v>
       </c>
       <c r="E7" t="n">
-        <v>29.36</v>
+        <v>264.52</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>2526</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H7" t="n">
-        <v>54</v>
+        <v>281</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C8" t="n">
-        <v>4190988309</v>
+        <v>9700005700</v>
       </c>
       <c r="D8" t="n">
-        <v>6224</v>
+        <v>4956</v>
       </c>
       <c r="E8" t="n">
-        <v>30.55</v>
+        <v>17.63</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -683,249 +683,249 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C9" t="n">
-        <v>9773660250</v>
+        <v>1841014603</v>
       </c>
       <c r="D9" t="n">
-        <v>4514</v>
+        <v>5801</v>
       </c>
       <c r="E9" t="n">
-        <v>264.52</v>
+        <v>38.14</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="G9" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>281</v>
+        <v>106</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C10" t="n">
-        <v>9773660250</v>
+        <v>9811363528</v>
       </c>
       <c r="D10" t="n">
-        <v>4514</v>
+        <v>3352</v>
       </c>
       <c r="E10" t="n">
-        <v>264.52</v>
+        <v>311.78</v>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>1448</v>
       </c>
       <c r="G10" t="n">
-        <v>96</v>
+        <v>433</v>
       </c>
       <c r="H10" t="n">
-        <v>281</v>
+        <v>1268</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C11" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D11" t="n">
-        <v>3617</v>
+        <v>4637</v>
       </c>
       <c r="E11" t="n">
-        <v>30.55</v>
+        <v>300.1</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>2619</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="H11" t="n">
-        <v>57</v>
+        <v>1173</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C12" t="n">
-        <v>2874903000</v>
+        <v>9630806627</v>
       </c>
       <c r="D12" t="n">
-        <v>1490</v>
+        <v>4546</v>
       </c>
       <c r="E12" t="n">
-        <v>28.63</v>
+        <v>358.77</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>3446</v>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>382</v>
       </c>
       <c r="H12" t="n">
-        <v>83</v>
+        <v>1119</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C13" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>2424</v>
       </c>
       <c r="E13" t="n">
-        <v>300.1</v>
+        <v>311.78</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>1448</v>
       </c>
       <c r="G13" t="n">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="H13" t="n">
-        <v>1173</v>
+        <v>1268</v>
       </c>
       <c r="I13" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C14" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D14" t="n">
-        <v>6082</v>
+        <v>6106</v>
       </c>
       <c r="E14" t="n">
-        <v>30.55</v>
+        <v>300.1</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>2619</v>
       </c>
       <c r="G14" t="n">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="H14" t="n">
-        <v>57</v>
+        <v>1173</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C15" t="n">
-        <v>9700005700</v>
+        <v>9811363528</v>
       </c>
       <c r="D15" t="n">
-        <v>5453</v>
+        <v>3749</v>
       </c>
       <c r="E15" t="n">
-        <v>17.63</v>
+        <v>311.78</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>1448</v>
       </c>
       <c r="G15" t="n">
+        <v>433</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1268</v>
+      </c>
+      <c r="I15" t="n">
         <v>30</v>
-      </c>
-      <c r="H15" t="n">
-        <v>88</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C16" t="n">
-        <v>8878077181</v>
+        <v>1841014603</v>
       </c>
       <c r="D16" t="n">
-        <v>3989</v>
+        <v>5592</v>
       </c>
       <c r="E16" t="n">
-        <v>539.88</v>
+        <v>38.14</v>
       </c>
       <c r="F16" t="n">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="G16" t="n">
-        <v>901</v>
+        <v>36</v>
       </c>
       <c r="H16" t="n">
-        <v>2640</v>
+        <v>106</v>
       </c>
       <c r="I16" t="n">
-        <v>92</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -938,84 +938,84 @@
         <v>63563817</v>
       </c>
       <c r="C17" t="n">
-        <v>4190988310</v>
+        <v>1841014603</v>
       </c>
       <c r="D17" t="n">
-        <v>228</v>
+        <v>1186</v>
       </c>
       <c r="E17" t="n">
-        <v>29.36</v>
+        <v>38.14</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="G17" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H17" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C18" t="n">
-        <v>9657930100</v>
+        <v>4190988310</v>
       </c>
       <c r="D18" t="n">
-        <v>5573</v>
+        <v>4713</v>
       </c>
       <c r="E18" t="n">
-        <v>4474.67</v>
+        <v>29.36</v>
       </c>
       <c r="F18" t="n">
-        <v>1208</v>
+        <v>118</v>
       </c>
       <c r="G18" t="n">
-        <v>4430</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>12980</v>
+        <v>54</v>
       </c>
       <c r="I18" t="n">
-        <v>453</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>63563817</v>
       </c>
       <c r="C19" t="n">
-        <v>4190988309</v>
+        <v>2874903000</v>
       </c>
       <c r="D19" t="n">
-        <v>6245</v>
+        <v>2574</v>
       </c>
       <c r="E19" t="n">
-        <v>30.55</v>
+        <v>28.63</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H19" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
@@ -1024,246 +1024,246 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C20" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D20" t="n">
-        <v>3179</v>
+        <v>4135</v>
       </c>
       <c r="E20" t="n">
-        <v>311.78</v>
+        <v>30.55</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="G20" t="n">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>1268</v>
+        <v>57</v>
       </c>
       <c r="I20" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>63563817</v>
       </c>
       <c r="C21" t="n">
-        <v>1841014603</v>
+        <v>2874903000</v>
       </c>
       <c r="D21" t="n">
-        <v>5267</v>
+        <v>4836</v>
       </c>
       <c r="E21" t="n">
-        <v>38.14</v>
+        <v>28.63</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>228</v>
       </c>
       <c r="G21" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H21" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C22" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D22" t="n">
-        <v>5061</v>
+        <v>1318</v>
       </c>
       <c r="E22" t="n">
-        <v>358.77</v>
+        <v>311.78</v>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>1448</v>
       </c>
       <c r="G22" t="n">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="H22" t="n">
-        <v>1119</v>
+        <v>1268</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C23" t="n">
-        <v>9657930100</v>
+        <v>9630806627</v>
       </c>
       <c r="D23" t="n">
-        <v>998</v>
+        <v>2997</v>
       </c>
       <c r="E23" t="n">
-        <v>4474.67</v>
+        <v>358.77</v>
       </c>
       <c r="F23" t="n">
-        <v>1208</v>
+        <v>3446</v>
       </c>
       <c r="G23" t="n">
-        <v>4430</v>
+        <v>382</v>
       </c>
       <c r="H23" t="n">
-        <v>12980</v>
+        <v>1119</v>
       </c>
       <c r="I23" t="n">
-        <v>453</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>63563817</v>
       </c>
       <c r="C24" t="n">
-        <v>2874903000</v>
+        <v>4190988309</v>
       </c>
       <c r="D24" t="n">
-        <v>2499</v>
+        <v>4135</v>
       </c>
       <c r="E24" t="n">
-        <v>28.63</v>
+        <v>30.55</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>265</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C25" t="n">
-        <v>4190988310</v>
+        <v>8878077181</v>
       </c>
       <c r="D25" t="n">
-        <v>5840</v>
+        <v>3989</v>
       </c>
       <c r="E25" t="n">
-        <v>29.36</v>
+        <v>539.88</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>1054</v>
       </c>
       <c r="G25" t="n">
-        <v>18</v>
+        <v>901</v>
       </c>
       <c r="H25" t="n">
-        <v>54</v>
+        <v>2640</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C26" t="n">
-        <v>9700005700</v>
+        <v>9630806627</v>
       </c>
       <c r="D26" t="n">
-        <v>5963</v>
+        <v>1824</v>
       </c>
       <c r="E26" t="n">
-        <v>17.63</v>
+        <v>358.77</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>3446</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>382</v>
       </c>
       <c r="H26" t="n">
-        <v>88</v>
+        <v>1119</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C27" t="n">
-        <v>4190988310</v>
+        <v>9700005700</v>
       </c>
       <c r="D27" t="n">
-        <v>1583</v>
+        <v>1900</v>
       </c>
       <c r="E27" t="n">
-        <v>29.36</v>
+        <v>17.63</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="G27" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -1272,122 +1272,122 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C28" t="n">
-        <v>9628223555</v>
+        <v>9657930100</v>
       </c>
       <c r="D28" t="n">
-        <v>1285</v>
+        <v>3587</v>
       </c>
       <c r="E28" t="n">
-        <v>300.1</v>
+        <v>4474.67</v>
       </c>
       <c r="F28" t="n">
-        <v>81</v>
+        <v>25139</v>
       </c>
       <c r="G28" t="n">
-        <v>400</v>
+        <v>4430</v>
       </c>
       <c r="H28" t="n">
-        <v>1173</v>
+        <v>12980</v>
       </c>
       <c r="I28" t="n">
-        <v>41</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>500635396</v>
       </c>
       <c r="C29" t="n">
-        <v>9700005700</v>
+        <v>9657930100</v>
       </c>
       <c r="D29" t="n">
-        <v>5453</v>
+        <v>6133</v>
       </c>
       <c r="E29" t="n">
-        <v>17.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>25139</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>4430</v>
       </c>
       <c r="H29" t="n">
-        <v>88</v>
+        <v>12980</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C30" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D30" t="n">
-        <v>5928</v>
+        <v>2397</v>
       </c>
       <c r="E30" t="n">
-        <v>311.78</v>
+        <v>30.55</v>
       </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="G30" t="n">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="H30" t="n">
-        <v>1268</v>
+        <v>57</v>
       </c>
       <c r="I30" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>63563817</v>
       </c>
       <c r="C31" t="n">
-        <v>2874903000</v>
+        <v>1841014603</v>
       </c>
       <c r="D31" t="n">
-        <v>4738</v>
+        <v>4186</v>
       </c>
       <c r="E31" t="n">
-        <v>28.63</v>
+        <v>38.14</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H31" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="I31" t="n">
         <v>3</v>
@@ -1396,69 +1396,69 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C32" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D32" t="n">
-        <v>4675</v>
+        <v>3989</v>
       </c>
       <c r="E32" t="n">
-        <v>38.14</v>
+        <v>539.88</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>1054</v>
       </c>
       <c r="G32" t="n">
-        <v>36</v>
+        <v>901</v>
       </c>
       <c r="H32" t="n">
-        <v>106</v>
+        <v>2640</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C33" t="n">
-        <v>9700005700</v>
+        <v>2526158329</v>
       </c>
       <c r="D33" t="n">
-        <v>6656</v>
+        <v>6604</v>
       </c>
       <c r="E33" t="n">
-        <v>17.63</v>
+        <v>12.66</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G33" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1468,13 +1468,13 @@
         <v>9657930100</v>
       </c>
       <c r="D34" t="n">
-        <v>6133</v>
+        <v>998</v>
       </c>
       <c r="E34" t="n">
         <v>4474.67</v>
       </c>
       <c r="F34" t="n">
-        <v>1208</v>
+        <v>25139</v>
       </c>
       <c r="G34" t="n">
         <v>4430</v>
@@ -1483,75 +1483,75 @@
         <v>12980</v>
       </c>
       <c r="I34" t="n">
-        <v>453</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>500635396</v>
       </c>
       <c r="C35" t="n">
-        <v>9773660250</v>
+        <v>9657930100</v>
       </c>
       <c r="D35" t="n">
-        <v>4514</v>
+        <v>998</v>
       </c>
       <c r="E35" t="n">
-        <v>264.52</v>
+        <v>4474.67</v>
       </c>
       <c r="F35" t="n">
-        <v>71</v>
+        <v>25139</v>
       </c>
       <c r="G35" t="n">
-        <v>96</v>
+        <v>4430</v>
       </c>
       <c r="H35" t="n">
-        <v>281</v>
+        <v>12980</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C36" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D36" t="n">
-        <v>3989</v>
+        <v>4514</v>
       </c>
       <c r="E36" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F36" t="n">
-        <v>146</v>
+        <v>2526</v>
       </c>
       <c r="G36" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H36" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I36" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1567,7 +1567,7 @@
         <v>4474.67</v>
       </c>
       <c r="F37" t="n">
-        <v>1208</v>
+        <v>25139</v>
       </c>
       <c r="G37" t="n">
         <v>4430</v>
@@ -1576,69 +1576,69 @@
         <v>12980</v>
       </c>
       <c r="I37" t="n">
-        <v>453</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>500635396</v>
       </c>
       <c r="C38" t="n">
-        <v>9657930100</v>
+        <v>9773660250</v>
       </c>
       <c r="D38" t="n">
-        <v>998</v>
+        <v>4514</v>
       </c>
       <c r="E38" t="n">
-        <v>4474.67</v>
+        <v>264.52</v>
       </c>
       <c r="F38" t="n">
-        <v>1208</v>
+        <v>2526</v>
       </c>
       <c r="G38" t="n">
-        <v>4430</v>
+        <v>96</v>
       </c>
       <c r="H38" t="n">
-        <v>12980</v>
+        <v>281</v>
       </c>
       <c r="I38" t="n">
-        <v>453</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C39" t="n">
-        <v>9628223555</v>
+        <v>4190988309</v>
       </c>
       <c r="D39" t="n">
-        <v>4865</v>
+        <v>6245</v>
       </c>
       <c r="E39" t="n">
-        <v>300.1</v>
+        <v>30.55</v>
       </c>
       <c r="F39" t="n">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="G39" t="n">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="H39" t="n">
-        <v>1173</v>
+        <v>57</v>
       </c>
       <c r="I39" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1651,25 +1651,25 @@
         <v>500635396</v>
       </c>
       <c r="C40" t="n">
-        <v>9657930100</v>
+        <v>9773660250</v>
       </c>
       <c r="D40" t="n">
-        <v>5874</v>
+        <v>4514</v>
       </c>
       <c r="E40" t="n">
-        <v>4474.67</v>
+        <v>264.52</v>
       </c>
       <c r="F40" t="n">
-        <v>1208</v>
+        <v>2526</v>
       </c>
       <c r="G40" t="n">
-        <v>4430</v>
+        <v>96</v>
       </c>
       <c r="H40" t="n">
-        <v>12980</v>
+        <v>281</v>
       </c>
       <c r="I40" t="n">
-        <v>453</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1685,13 +1685,13 @@
         <v>2874903000</v>
       </c>
       <c r="D41" t="n">
-        <v>2596</v>
+        <v>6242</v>
       </c>
       <c r="E41" t="n">
         <v>28.63</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="G41" t="n">
         <v>28</v>
@@ -1700,13 +1700,13 @@
         <v>83</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1716,13 +1716,13 @@
         <v>1841014603</v>
       </c>
       <c r="D42" t="n">
-        <v>3304</v>
+        <v>2505</v>
       </c>
       <c r="E42" t="n">
         <v>38.14</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>205</v>
       </c>
       <c r="G42" t="n">
         <v>36</v>
@@ -1731,38 +1731,38 @@
         <v>106</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C43" t="n">
-        <v>9700005700</v>
+        <v>2874903000</v>
       </c>
       <c r="D43" t="n">
-        <v>5248</v>
+        <v>2574</v>
       </c>
       <c r="E43" t="n">
-        <v>17.63</v>
+        <v>28.63</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>228</v>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H43" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1772,307 +1772,307 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C44" t="n">
-        <v>9773660250</v>
+        <v>9630806627</v>
       </c>
       <c r="D44" t="n">
-        <v>4514</v>
+        <v>6004</v>
       </c>
       <c r="E44" t="n">
-        <v>264.52</v>
+        <v>358.77</v>
       </c>
       <c r="F44" t="n">
-        <v>71</v>
+        <v>3446</v>
       </c>
       <c r="G44" t="n">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="H44" t="n">
-        <v>281</v>
+        <v>1119</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C45" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D45" t="n">
-        <v>3716</v>
+        <v>2397</v>
       </c>
       <c r="E45" t="n">
-        <v>311.78</v>
+        <v>30.55</v>
       </c>
       <c r="F45" t="n">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="G45" t="n">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="H45" t="n">
-        <v>1268</v>
+        <v>57</v>
       </c>
       <c r="I45" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>500635396</v>
       </c>
       <c r="C46" t="n">
-        <v>9657930100</v>
+        <v>9773660250</v>
       </c>
       <c r="D46" t="n">
-        <v>3587</v>
+        <v>4514</v>
       </c>
       <c r="E46" t="n">
-        <v>4474.67</v>
+        <v>264.52</v>
       </c>
       <c r="F46" t="n">
-        <v>1208</v>
+        <v>2526</v>
       </c>
       <c r="G46" t="n">
-        <v>4430</v>
+        <v>96</v>
       </c>
       <c r="H46" t="n">
-        <v>12980</v>
+        <v>281</v>
       </c>
       <c r="I46" t="n">
-        <v>453</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>500635396</v>
       </c>
       <c r="C47" t="n">
-        <v>9773660250</v>
+        <v>9700005700</v>
       </c>
       <c r="D47" t="n">
-        <v>4514</v>
+        <v>5963</v>
       </c>
       <c r="E47" t="n">
-        <v>264.52</v>
+        <v>17.63</v>
       </c>
       <c r="F47" t="n">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="G47" t="n">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="H47" t="n">
-        <v>281</v>
+        <v>88</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>63563817</v>
       </c>
       <c r="C48" t="n">
-        <v>2526158329</v>
+        <v>1841014603</v>
       </c>
       <c r="D48" t="n">
-        <v>3286</v>
+        <v>3304</v>
       </c>
       <c r="E48" t="n">
-        <v>12.66</v>
+        <v>38.14</v>
       </c>
       <c r="F48" t="n">
+        <v>205</v>
+      </c>
+      <c r="G48" t="n">
+        <v>36</v>
+      </c>
+      <c r="H48" t="n">
+        <v>106</v>
+      </c>
+      <c r="I48" t="n">
         <v>3</v>
-      </c>
-      <c r="G48" t="n">
-        <v>8</v>
-      </c>
-      <c r="H48" t="n">
-        <v>24</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>63563817</v>
       </c>
       <c r="C49" t="n">
-        <v>2874903000</v>
+        <v>4190988309</v>
       </c>
       <c r="D49" t="n">
-        <v>2574</v>
+        <v>3617</v>
       </c>
       <c r="E49" t="n">
-        <v>28.63</v>
+        <v>30.55</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>265</v>
       </c>
       <c r="G49" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H49" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C50" t="n">
-        <v>4190988309</v>
+        <v>9657930100</v>
       </c>
       <c r="D50" t="n">
-        <v>6224</v>
+        <v>6133</v>
       </c>
       <c r="E50" t="n">
-        <v>30.55</v>
+        <v>4474.67</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>25139</v>
       </c>
       <c r="G50" t="n">
-        <v>19</v>
+        <v>4430</v>
       </c>
       <c r="H50" t="n">
-        <v>57</v>
+        <v>12980</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C51" t="n">
-        <v>9811363528</v>
+        <v>2874903000</v>
       </c>
       <c r="D51" t="n">
-        <v>4639</v>
+        <v>2574</v>
       </c>
       <c r="E51" t="n">
-        <v>311.78</v>
+        <v>28.63</v>
       </c>
       <c r="F51" t="n">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="G51" t="n">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="H51" t="n">
-        <v>1268</v>
+        <v>83</v>
       </c>
       <c r="I51" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C52" t="n">
-        <v>4190988310</v>
+        <v>9657930100</v>
       </c>
       <c r="D52" t="n">
-        <v>2294</v>
+        <v>5166</v>
       </c>
       <c r="E52" t="n">
-        <v>29.36</v>
+        <v>4474.67</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>25139</v>
       </c>
       <c r="G52" t="n">
-        <v>18</v>
+        <v>4430</v>
       </c>
       <c r="H52" t="n">
-        <v>54</v>
+        <v>12980</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>63563817</v>
       </c>
       <c r="C53" t="n">
-        <v>2874903000</v>
+        <v>4190988310</v>
       </c>
       <c r="D53" t="n">
-        <v>648</v>
+        <v>3818</v>
       </c>
       <c r="E53" t="n">
-        <v>28.63</v>
+        <v>29.36</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="G53" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2088,13 +2088,13 @@
         <v>9811363528</v>
       </c>
       <c r="D54" t="n">
-        <v>3043</v>
+        <v>2288</v>
       </c>
       <c r="E54" t="n">
         <v>311.78</v>
       </c>
       <c r="F54" t="n">
-        <v>84</v>
+        <v>1448</v>
       </c>
       <c r="G54" t="n">
         <v>433</v>
@@ -2103,7 +2103,7 @@
         <v>1268</v>
       </c>
       <c r="I54" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -2119,13 +2119,13 @@
         <v>8878077181</v>
       </c>
       <c r="D55" t="n">
-        <v>3989</v>
+        <v>1048</v>
       </c>
       <c r="E55" t="n">
         <v>539.88</v>
       </c>
       <c r="F55" t="n">
-        <v>146</v>
+        <v>1054</v>
       </c>
       <c r="G55" t="n">
         <v>901</v>
@@ -2134,100 +2134,100 @@
         <v>2640</v>
       </c>
       <c r="I55" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C56" t="n">
-        <v>9773660250</v>
+        <v>4190988310</v>
       </c>
       <c r="D56" t="n">
-        <v>4514</v>
+        <v>5840</v>
       </c>
       <c r="E56" t="n">
-        <v>264.52</v>
+        <v>29.36</v>
       </c>
       <c r="F56" t="n">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="G56" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="H56" t="n">
-        <v>281</v>
+        <v>54</v>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C57" t="n">
-        <v>9630806627</v>
+        <v>4190988310</v>
       </c>
       <c r="D57" t="n">
-        <v>4016</v>
+        <v>3501</v>
       </c>
       <c r="E57" t="n">
-        <v>358.77</v>
+        <v>29.36</v>
       </c>
       <c r="F57" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G57" t="n">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="H57" t="n">
-        <v>1119</v>
+        <v>54</v>
       </c>
       <c r="I57" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C58" t="n">
-        <v>8878077181</v>
+        <v>2874903000</v>
       </c>
       <c r="D58" t="n">
-        <v>1048</v>
+        <v>2669</v>
       </c>
       <c r="E58" t="n">
-        <v>539.88</v>
+        <v>28.63</v>
       </c>
       <c r="F58" t="n">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="G58" t="n">
-        <v>901</v>
+        <v>28</v>
       </c>
       <c r="H58" t="n">
-        <v>2640</v>
+        <v>83</v>
       </c>
       <c r="I58" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2237,127 +2237,127 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C59" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D59" t="n">
-        <v>3989</v>
+        <v>4514</v>
       </c>
       <c r="E59" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F59" t="n">
-        <v>146</v>
+        <v>2526</v>
       </c>
       <c r="G59" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H59" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I59" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C60" t="n">
-        <v>9630806627</v>
+        <v>4190988310</v>
       </c>
       <c r="D60" t="n">
-        <v>4606</v>
+        <v>4155</v>
       </c>
       <c r="E60" t="n">
-        <v>358.77</v>
+        <v>29.36</v>
       </c>
       <c r="F60" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G60" t="n">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="H60" t="n">
-        <v>1119</v>
+        <v>54</v>
       </c>
       <c r="I60" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C61" t="n">
-        <v>8878077181</v>
+        <v>9700005700</v>
       </c>
       <c r="D61" t="n">
-        <v>1048</v>
+        <v>5453</v>
       </c>
       <c r="E61" t="n">
-        <v>539.88</v>
+        <v>17.63</v>
       </c>
       <c r="F61" t="n">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G61" t="n">
-        <v>901</v>
+        <v>30</v>
       </c>
       <c r="H61" t="n">
-        <v>2640</v>
+        <v>88</v>
       </c>
       <c r="I61" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>63563817</v>
       </c>
       <c r="C62" t="n">
-        <v>4190988310</v>
+        <v>4190988309</v>
       </c>
       <c r="D62" t="n">
-        <v>3818</v>
+        <v>6082</v>
       </c>
       <c r="E62" t="n">
-        <v>29.36</v>
+        <v>30.55</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>265</v>
       </c>
       <c r="G62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H62" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2367,13 +2367,13 @@
         <v>1841014603</v>
       </c>
       <c r="D63" t="n">
-        <v>2889</v>
+        <v>5267</v>
       </c>
       <c r="E63" t="n">
         <v>38.14</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>205</v>
       </c>
       <c r="G63" t="n">
         <v>36</v>
@@ -2382,323 +2382,323 @@
         <v>106</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>63563817</v>
       </c>
       <c r="C64" t="n">
-        <v>4190988310</v>
+        <v>1841014603</v>
       </c>
       <c r="D64" t="n">
-        <v>3501</v>
+        <v>3169</v>
       </c>
       <c r="E64" t="n">
-        <v>29.36</v>
+        <v>38.14</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="G64" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H64" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C65" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D65" t="n">
-        <v>5862</v>
+        <v>61</v>
       </c>
       <c r="E65" t="n">
-        <v>300.1</v>
+        <v>311.78</v>
       </c>
       <c r="F65" t="n">
-        <v>81</v>
+        <v>1448</v>
       </c>
       <c r="G65" t="n">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="H65" t="n">
-        <v>1173</v>
+        <v>1268</v>
       </c>
       <c r="I65" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C66" t="n">
-        <v>1841014603</v>
+        <v>9773660250</v>
       </c>
       <c r="D66" t="n">
-        <v>2889</v>
+        <v>4514</v>
       </c>
       <c r="E66" t="n">
-        <v>38.14</v>
+        <v>264.52</v>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>2526</v>
       </c>
       <c r="G66" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="H66" t="n">
-        <v>106</v>
+        <v>281</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C67" t="n">
-        <v>9811363528</v>
+        <v>9700005700</v>
       </c>
       <c r="D67" t="n">
-        <v>2655</v>
+        <v>5248</v>
       </c>
       <c r="E67" t="n">
-        <v>311.78</v>
+        <v>17.63</v>
       </c>
       <c r="F67" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="G67" t="n">
-        <v>433</v>
+        <v>30</v>
       </c>
       <c r="H67" t="n">
-        <v>1268</v>
+        <v>88</v>
       </c>
       <c r="I67" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>495817671</v>
+        <v>500635396</v>
       </c>
       <c r="C68" t="n">
-        <v>9630806627</v>
+        <v>9700005700</v>
       </c>
       <c r="D68" t="n">
-        <v>5273</v>
+        <v>5248</v>
       </c>
       <c r="E68" t="n">
-        <v>358.77</v>
+        <v>17.63</v>
       </c>
       <c r="F68" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="G68" t="n">
-        <v>382</v>
+        <v>30</v>
       </c>
       <c r="H68" t="n">
-        <v>1119</v>
+        <v>88</v>
       </c>
       <c r="I68" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>63563817</v>
       </c>
       <c r="C69" t="n">
-        <v>2874903000</v>
+        <v>4190988310</v>
       </c>
       <c r="D69" t="n">
-        <v>2574</v>
+        <v>6364</v>
       </c>
       <c r="E69" t="n">
-        <v>28.63</v>
+        <v>29.36</v>
       </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="G69" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H69" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>495817671</v>
+        <v>525368335</v>
       </c>
       <c r="C70" t="n">
-        <v>9630806627</v>
+        <v>9811363528</v>
       </c>
       <c r="D70" t="n">
-        <v>1853</v>
+        <v>3843</v>
       </c>
       <c r="E70" t="n">
-        <v>358.77</v>
+        <v>311.78</v>
       </c>
       <c r="F70" t="n">
-        <v>97</v>
+        <v>1448</v>
       </c>
       <c r="G70" t="n">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="H70" t="n">
-        <v>1119</v>
+        <v>1268</v>
       </c>
       <c r="I70" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C71" t="n">
-        <v>9773660250</v>
+        <v>2874903000</v>
       </c>
       <c r="D71" t="n">
-        <v>4514</v>
+        <v>5995</v>
       </c>
       <c r="E71" t="n">
-        <v>264.52</v>
+        <v>28.63</v>
       </c>
       <c r="F71" t="n">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="G71" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="H71" t="n">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C72" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D72" t="n">
-        <v>6245</v>
+        <v>734</v>
       </c>
       <c r="E72" t="n">
-        <v>30.55</v>
+        <v>300.1</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>2619</v>
       </c>
       <c r="G72" t="n">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="H72" t="n">
-        <v>57</v>
+        <v>1173</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C73" t="n">
-        <v>9628223555</v>
+        <v>4190988309</v>
       </c>
       <c r="D73" t="n">
-        <v>2093</v>
+        <v>6082</v>
       </c>
       <c r="E73" t="n">
-        <v>300.1</v>
+        <v>30.55</v>
       </c>
       <c r="F73" t="n">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="G73" t="n">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="H73" t="n">
-        <v>1173</v>
+        <v>57</v>
       </c>
       <c r="I73" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2708,13 +2708,13 @@
         <v>9700005700</v>
       </c>
       <c r="D74" t="n">
-        <v>4956</v>
+        <v>5453</v>
       </c>
       <c r="E74" t="n">
         <v>17.63</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="G74" t="n">
         <v>30</v>
@@ -2723,168 +2723,168 @@
         <v>88</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C75" t="n">
-        <v>9700005700</v>
+        <v>9628223555</v>
       </c>
       <c r="D75" t="n">
-        <v>1900</v>
+        <v>700</v>
       </c>
       <c r="E75" t="n">
-        <v>17.63</v>
+        <v>300.1</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>2619</v>
       </c>
       <c r="G75" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="H75" t="n">
-        <v>88</v>
+        <v>1173</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C76" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D76" t="n">
-        <v>3692</v>
+        <v>1048</v>
       </c>
       <c r="E76" t="n">
-        <v>311.78</v>
+        <v>539.88</v>
       </c>
       <c r="F76" t="n">
-        <v>84</v>
+        <v>1054</v>
       </c>
       <c r="G76" t="n">
-        <v>433</v>
+        <v>901</v>
       </c>
       <c r="H76" t="n">
-        <v>1268</v>
+        <v>2640</v>
       </c>
       <c r="I76" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C77" t="n">
-        <v>9628223555</v>
+        <v>9773660250</v>
       </c>
       <c r="D77" t="n">
-        <v>1719</v>
+        <v>4514</v>
       </c>
       <c r="E77" t="n">
-        <v>300.1</v>
+        <v>264.52</v>
       </c>
       <c r="F77" t="n">
-        <v>81</v>
+        <v>2526</v>
       </c>
       <c r="G77" t="n">
-        <v>400</v>
+        <v>96</v>
       </c>
       <c r="H77" t="n">
-        <v>1173</v>
+        <v>281</v>
       </c>
       <c r="I77" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C78" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D78" t="n">
-        <v>6130</v>
+        <v>2501</v>
       </c>
       <c r="E78" t="n">
-        <v>311.78</v>
+        <v>358.77</v>
       </c>
       <c r="F78" t="n">
-        <v>84</v>
+        <v>3446</v>
       </c>
       <c r="G78" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H78" t="n">
-        <v>1268</v>
+        <v>1119</v>
       </c>
       <c r="I78" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>495403620</v>
       </c>
       <c r="C79" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D79" t="n">
-        <v>1465</v>
+        <v>3989</v>
       </c>
       <c r="E79" t="n">
-        <v>300.1</v>
+        <v>539.88</v>
       </c>
       <c r="F79" t="n">
-        <v>81</v>
+        <v>1054</v>
       </c>
       <c r="G79" t="n">
-        <v>400</v>
+        <v>901</v>
       </c>
       <c r="H79" t="n">
-        <v>1173</v>
+        <v>2640</v>
       </c>
       <c r="I79" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2894,13 +2894,13 @@
         <v>9700005700</v>
       </c>
       <c r="D80" t="n">
-        <v>5963</v>
+        <v>5453</v>
       </c>
       <c r="E80" t="n">
         <v>17.63</v>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="G80" t="n">
         <v>30</v>
@@ -2909,317 +2909,317 @@
         <v>88</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C81" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D81" t="n">
-        <v>3617</v>
+        <v>4736</v>
       </c>
       <c r="E81" t="n">
-        <v>30.55</v>
+        <v>311.78</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>1448</v>
       </c>
       <c r="G81" t="n">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="H81" t="n">
-        <v>57</v>
+        <v>1268</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C82" t="n">
-        <v>1841014603</v>
+        <v>8878077181</v>
       </c>
       <c r="D82" t="n">
-        <v>4186</v>
+        <v>3989</v>
       </c>
       <c r="E82" t="n">
-        <v>38.14</v>
+        <v>539.88</v>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>1054</v>
       </c>
       <c r="G82" t="n">
-        <v>36</v>
+        <v>901</v>
       </c>
       <c r="H82" t="n">
-        <v>106</v>
+        <v>2640</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C83" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D83" t="n">
-        <v>4713</v>
+        <v>3567</v>
       </c>
       <c r="E83" t="n">
-        <v>38.14</v>
+        <v>300.1</v>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>2619</v>
       </c>
       <c r="G83" t="n">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="H83" t="n">
-        <v>106</v>
+        <v>1173</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C84" t="n">
-        <v>9630806627</v>
+        <v>4190988310</v>
       </c>
       <c r="D84" t="n">
-        <v>3913</v>
+        <v>2212</v>
       </c>
       <c r="E84" t="n">
-        <v>358.77</v>
+        <v>29.36</v>
       </c>
       <c r="F84" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G84" t="n">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="H84" t="n">
-        <v>1119</v>
+        <v>54</v>
       </c>
       <c r="I84" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C85" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D85" t="n">
-        <v>3989</v>
+        <v>6538</v>
       </c>
       <c r="E85" t="n">
-        <v>539.88</v>
+        <v>358.77</v>
       </c>
       <c r="F85" t="n">
-        <v>146</v>
+        <v>3446</v>
       </c>
       <c r="G85" t="n">
-        <v>901</v>
+        <v>382</v>
       </c>
       <c r="H85" t="n">
-        <v>2640</v>
+        <v>1119</v>
       </c>
       <c r="I85" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C86" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D86" t="n">
-        <v>5267</v>
+        <v>1531</v>
       </c>
       <c r="E86" t="n">
-        <v>38.14</v>
+        <v>300.1</v>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>2619</v>
       </c>
       <c r="G86" t="n">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="H86" t="n">
-        <v>106</v>
+        <v>1173</v>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C87" t="n">
-        <v>9773660250</v>
+        <v>9630806627</v>
       </c>
       <c r="D87" t="n">
-        <v>4514</v>
+        <v>2195</v>
       </c>
       <c r="E87" t="n">
-        <v>264.52</v>
+        <v>358.77</v>
       </c>
       <c r="F87" t="n">
-        <v>71</v>
+        <v>3446</v>
       </c>
       <c r="G87" t="n">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="H87" t="n">
-        <v>281</v>
+        <v>1119</v>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C88" t="n">
-        <v>9630806627</v>
+        <v>4190988310</v>
       </c>
       <c r="D88" t="n">
-        <v>292</v>
+        <v>1583</v>
       </c>
       <c r="E88" t="n">
-        <v>358.77</v>
+        <v>29.36</v>
       </c>
       <c r="F88" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G88" t="n">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="H88" t="n">
-        <v>1119</v>
+        <v>54</v>
       </c>
       <c r="I88" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C89" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D89" t="n">
-        <v>6210</v>
+        <v>5199</v>
       </c>
       <c r="E89" t="n">
-        <v>300.1</v>
+        <v>358.77</v>
       </c>
       <c r="F89" t="n">
-        <v>81</v>
+        <v>3446</v>
       </c>
       <c r="G89" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="H89" t="n">
-        <v>1173</v>
+        <v>1119</v>
       </c>
       <c r="I89" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C90" t="n">
-        <v>4190988309</v>
+        <v>9628223555</v>
       </c>
       <c r="D90" t="n">
-        <v>6082</v>
+        <v>1373</v>
       </c>
       <c r="E90" t="n">
-        <v>30.55</v>
+        <v>300.1</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>2619</v>
       </c>
       <c r="G90" t="n">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="H90" t="n">
-        <v>57</v>
+        <v>1173</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result3.xlsx
+++ b/results/excel/result3.xlsx
@@ -466,187 +466,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C2" t="n">
-        <v>8878077181</v>
+        <v>9700005700</v>
       </c>
       <c r="D2" t="n">
-        <v>1048</v>
+        <v>4956</v>
       </c>
       <c r="E2" t="n">
-        <v>539.88</v>
+        <v>17.63</v>
       </c>
       <c r="F2" t="n">
-        <v>1054</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>901</v>
+        <v>30</v>
       </c>
       <c r="H2" t="n">
-        <v>2640</v>
+        <v>88</v>
       </c>
       <c r="I2" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C3" t="n">
-        <v>9657930100</v>
+        <v>9811363528</v>
       </c>
       <c r="D3" t="n">
-        <v>998</v>
+        <v>588</v>
       </c>
       <c r="E3" t="n">
-        <v>4474.67</v>
+        <v>311.78</v>
       </c>
       <c r="F3" t="n">
-        <v>25139</v>
+        <v>1448</v>
       </c>
       <c r="G3" t="n">
-        <v>4430</v>
+        <v>433</v>
       </c>
       <c r="H3" t="n">
-        <v>12980</v>
+        <v>1268</v>
       </c>
       <c r="I3" t="n">
-        <v>310</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C4" t="n">
-        <v>9628223555</v>
+        <v>9657930100</v>
       </c>
       <c r="D4" t="n">
-        <v>6542</v>
+        <v>998</v>
       </c>
       <c r="E4" t="n">
-        <v>300.1</v>
+        <v>4474.67</v>
       </c>
       <c r="F4" t="n">
-        <v>2619</v>
+        <v>25139</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>4430</v>
       </c>
       <c r="H4" t="n">
-        <v>1173</v>
+        <v>12980</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C5" t="n">
-        <v>2874903000</v>
+        <v>9657930100</v>
       </c>
       <c r="D5" t="n">
-        <v>2959</v>
+        <v>6452</v>
       </c>
       <c r="E5" t="n">
-        <v>28.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F5" t="n">
-        <v>228</v>
+        <v>25139</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>4430</v>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>12980</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C6" t="n">
-        <v>8878077181</v>
+        <v>9700005700</v>
       </c>
       <c r="D6" t="n">
-        <v>3989</v>
+        <v>4956</v>
       </c>
       <c r="E6" t="n">
-        <v>539.88</v>
+        <v>17.63</v>
       </c>
       <c r="F6" t="n">
-        <v>1054</v>
+        <v>128</v>
       </c>
       <c r="G6" t="n">
-        <v>901</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>2640</v>
+        <v>88</v>
       </c>
       <c r="I6" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C7" t="n">
-        <v>9773660250</v>
+        <v>4190988309</v>
       </c>
       <c r="D7" t="n">
-        <v>4514</v>
+        <v>3617</v>
       </c>
       <c r="E7" t="n">
-        <v>264.52</v>
+        <v>30.55</v>
       </c>
       <c r="F7" t="n">
-        <v>2526</v>
+        <v>265</v>
       </c>
       <c r="G7" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -656,375 +656,375 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C8" t="n">
-        <v>9700005700</v>
+        <v>9628223555</v>
       </c>
       <c r="D8" t="n">
-        <v>4956</v>
+        <v>2551</v>
       </c>
       <c r="E8" t="n">
-        <v>17.63</v>
+        <v>300.1</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>2619</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>1173</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>63563817</v>
       </c>
       <c r="C9" t="n">
-        <v>1841014603</v>
+        <v>4190988309</v>
       </c>
       <c r="D9" t="n">
-        <v>5801</v>
+        <v>6082</v>
       </c>
       <c r="E9" t="n">
-        <v>38.14</v>
+        <v>30.55</v>
       </c>
       <c r="F9" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C10" t="n">
-        <v>9811363528</v>
+        <v>2874903000</v>
       </c>
       <c r="D10" t="n">
-        <v>3352</v>
+        <v>2596</v>
       </c>
       <c r="E10" t="n">
-        <v>311.78</v>
+        <v>28.63</v>
       </c>
       <c r="F10" t="n">
-        <v>1448</v>
+        <v>228</v>
       </c>
       <c r="G10" t="n">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>1268</v>
+        <v>83</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C11" t="n">
-        <v>9628223555</v>
+        <v>8878077181</v>
       </c>
       <c r="D11" t="n">
-        <v>4637</v>
+        <v>1048</v>
       </c>
       <c r="E11" t="n">
-        <v>300.1</v>
+        <v>539.88</v>
       </c>
       <c r="F11" t="n">
-        <v>2619</v>
+        <v>1054</v>
       </c>
       <c r="G11" t="n">
-        <v>400</v>
+        <v>901</v>
       </c>
       <c r="H11" t="n">
-        <v>1173</v>
+        <v>2640</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C12" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D12" t="n">
-        <v>4546</v>
+        <v>5862</v>
       </c>
       <c r="E12" t="n">
-        <v>358.77</v>
+        <v>300.1</v>
       </c>
       <c r="F12" t="n">
-        <v>3446</v>
+        <v>2619</v>
       </c>
       <c r="G12" t="n">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="H12" t="n">
-        <v>1119</v>
+        <v>1173</v>
       </c>
       <c r="I12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C13" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D13" t="n">
-        <v>2424</v>
+        <v>6224</v>
       </c>
       <c r="E13" t="n">
-        <v>311.78</v>
+        <v>30.55</v>
       </c>
       <c r="F13" t="n">
-        <v>1448</v>
+        <v>265</v>
       </c>
       <c r="G13" t="n">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>1268</v>
+        <v>57</v>
       </c>
       <c r="I13" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C14" t="n">
-        <v>9628223555</v>
+        <v>2526158329</v>
       </c>
       <c r="D14" t="n">
-        <v>6106</v>
+        <v>934</v>
       </c>
       <c r="E14" t="n">
-        <v>300.1</v>
+        <v>12.66</v>
       </c>
       <c r="F14" t="n">
-        <v>2619</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>1173</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C15" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D15" t="n">
-        <v>3749</v>
+        <v>2125</v>
       </c>
       <c r="E15" t="n">
-        <v>311.78</v>
+        <v>358.77</v>
       </c>
       <c r="F15" t="n">
-        <v>1448</v>
+        <v>3446</v>
       </c>
       <c r="G15" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H15" t="n">
-        <v>1268</v>
+        <v>1119</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C16" t="n">
-        <v>1841014603</v>
+        <v>9657930100</v>
       </c>
       <c r="D16" t="n">
-        <v>5592</v>
+        <v>6133</v>
       </c>
       <c r="E16" t="n">
-        <v>38.14</v>
+        <v>4474.67</v>
       </c>
       <c r="F16" t="n">
-        <v>205</v>
+        <v>25139</v>
       </c>
       <c r="G16" t="n">
-        <v>36</v>
+        <v>4430</v>
       </c>
       <c r="H16" t="n">
-        <v>106</v>
+        <v>12980</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C17" t="n">
-        <v>1841014603</v>
+        <v>9773660250</v>
       </c>
       <c r="D17" t="n">
-        <v>1186</v>
+        <v>4514</v>
       </c>
       <c r="E17" t="n">
-        <v>38.14</v>
+        <v>264.52</v>
       </c>
       <c r="F17" t="n">
-        <v>205</v>
+        <v>2526</v>
       </c>
       <c r="G17" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="H17" t="n">
-        <v>106</v>
+        <v>281</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C18" t="n">
-        <v>4190988310</v>
+        <v>9628223555</v>
       </c>
       <c r="D18" t="n">
-        <v>4713</v>
+        <v>6017</v>
       </c>
       <c r="E18" t="n">
-        <v>29.36</v>
+        <v>300.1</v>
       </c>
       <c r="F18" t="n">
-        <v>118</v>
+        <v>2619</v>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="H18" t="n">
-        <v>54</v>
+        <v>1173</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C19" t="n">
-        <v>2874903000</v>
+        <v>9657930100</v>
       </c>
       <c r="D19" t="n">
-        <v>2574</v>
+        <v>5573</v>
       </c>
       <c r="E19" t="n">
-        <v>28.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F19" t="n">
-        <v>228</v>
+        <v>25139</v>
       </c>
       <c r="G19" t="n">
-        <v>28</v>
+        <v>4430</v>
       </c>
       <c r="H19" t="n">
-        <v>83</v>
+        <v>12980</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1034,7 +1034,7 @@
         <v>4190988309</v>
       </c>
       <c r="D20" t="n">
-        <v>4135</v>
+        <v>6224</v>
       </c>
       <c r="E20" t="n">
         <v>30.55</v>
@@ -1059,25 +1059,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C21" t="n">
-        <v>2874903000</v>
+        <v>9700005700</v>
       </c>
       <c r="D21" t="n">
-        <v>4836</v>
+        <v>4956</v>
       </c>
       <c r="E21" t="n">
-        <v>28.63</v>
+        <v>17.63</v>
       </c>
       <c r="F21" t="n">
-        <v>228</v>
+        <v>128</v>
       </c>
       <c r="G21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H21" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
@@ -1086,162 +1086,162 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C22" t="n">
-        <v>9811363528</v>
+        <v>4190988310</v>
       </c>
       <c r="D22" t="n">
-        <v>1318</v>
+        <v>2212</v>
       </c>
       <c r="E22" t="n">
-        <v>311.78</v>
+        <v>29.36</v>
       </c>
       <c r="F22" t="n">
-        <v>1448</v>
+        <v>118</v>
       </c>
       <c r="G22" t="n">
-        <v>433</v>
+        <v>18</v>
       </c>
       <c r="H22" t="n">
-        <v>1268</v>
+        <v>54</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C23" t="n">
-        <v>9630806627</v>
+        <v>9700005700</v>
       </c>
       <c r="D23" t="n">
-        <v>2997</v>
+        <v>5453</v>
       </c>
       <c r="E23" t="n">
-        <v>358.77</v>
+        <v>17.63</v>
       </c>
       <c r="F23" t="n">
-        <v>3446</v>
+        <v>128</v>
       </c>
       <c r="G23" t="n">
-        <v>382</v>
+        <v>30</v>
       </c>
       <c r="H23" t="n">
-        <v>1119</v>
+        <v>88</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C24" t="n">
-        <v>4190988309</v>
+        <v>9773660250</v>
       </c>
       <c r="D24" t="n">
-        <v>4135</v>
+        <v>4514</v>
       </c>
       <c r="E24" t="n">
-        <v>30.55</v>
+        <v>264.52</v>
       </c>
       <c r="F24" t="n">
-        <v>265</v>
+        <v>2526</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H24" t="n">
-        <v>57</v>
+        <v>281</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C25" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D25" t="n">
-        <v>3989</v>
+        <v>2890</v>
       </c>
       <c r="E25" t="n">
-        <v>539.88</v>
+        <v>311.78</v>
       </c>
       <c r="F25" t="n">
-        <v>1054</v>
+        <v>1448</v>
       </c>
       <c r="G25" t="n">
-        <v>901</v>
+        <v>433</v>
       </c>
       <c r="H25" t="n">
-        <v>2640</v>
+        <v>1268</v>
       </c>
       <c r="I25" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>495817671</v>
+        <v>500635396</v>
       </c>
       <c r="C26" t="n">
-        <v>9630806627</v>
+        <v>9773660250</v>
       </c>
       <c r="D26" t="n">
-        <v>1824</v>
+        <v>4514</v>
       </c>
       <c r="E26" t="n">
-        <v>358.77</v>
+        <v>264.52</v>
       </c>
       <c r="F26" t="n">
-        <v>3446</v>
+        <v>2526</v>
       </c>
       <c r="G26" t="n">
-        <v>382</v>
+        <v>96</v>
       </c>
       <c r="H26" t="n">
-        <v>1119</v>
+        <v>281</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1251,7 +1251,7 @@
         <v>9700005700</v>
       </c>
       <c r="D27" t="n">
-        <v>1900</v>
+        <v>5248</v>
       </c>
       <c r="E27" t="n">
         <v>17.63</v>
@@ -1272,69 +1272,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C28" t="n">
-        <v>9657930100</v>
+        <v>2874903000</v>
       </c>
       <c r="D28" t="n">
-        <v>3587</v>
+        <v>2959</v>
       </c>
       <c r="E28" t="n">
-        <v>4474.67</v>
+        <v>28.63</v>
       </c>
       <c r="F28" t="n">
-        <v>25139</v>
+        <v>228</v>
       </c>
       <c r="G28" t="n">
-        <v>4430</v>
+        <v>28</v>
       </c>
       <c r="H28" t="n">
-        <v>12980</v>
+        <v>83</v>
       </c>
       <c r="I28" t="n">
-        <v>310</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C29" t="n">
-        <v>9657930100</v>
+        <v>8878077181</v>
       </c>
       <c r="D29" t="n">
-        <v>6133</v>
+        <v>1048</v>
       </c>
       <c r="E29" t="n">
-        <v>4474.67</v>
+        <v>539.88</v>
       </c>
       <c r="F29" t="n">
-        <v>25139</v>
+        <v>1054</v>
       </c>
       <c r="G29" t="n">
-        <v>4430</v>
+        <v>901</v>
       </c>
       <c r="H29" t="n">
-        <v>12980</v>
+        <v>2640</v>
       </c>
       <c r="I29" t="n">
-        <v>310</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1365,7 +1365,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1375,7 +1375,7 @@
         <v>1841014603</v>
       </c>
       <c r="D31" t="n">
-        <v>4186</v>
+        <v>6414</v>
       </c>
       <c r="E31" t="n">
         <v>38.14</v>
@@ -1396,32 +1396,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C32" t="n">
-        <v>8878077181</v>
+        <v>9657930100</v>
       </c>
       <c r="D32" t="n">
-        <v>3989</v>
+        <v>5166</v>
       </c>
       <c r="E32" t="n">
-        <v>539.88</v>
+        <v>4474.67</v>
       </c>
       <c r="F32" t="n">
-        <v>1054</v>
+        <v>25139</v>
       </c>
       <c r="G32" t="n">
-        <v>901</v>
+        <v>4430</v>
       </c>
       <c r="H32" t="n">
-        <v>2640</v>
+        <v>12980</v>
       </c>
       <c r="I32" t="n">
-        <v>63</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33">
@@ -1434,22 +1434,22 @@
         <v>63563817</v>
       </c>
       <c r="C33" t="n">
-        <v>2526158329</v>
+        <v>4190988310</v>
       </c>
       <c r="D33" t="n">
-        <v>6604</v>
+        <v>1108</v>
       </c>
       <c r="E33" t="n">
-        <v>12.66</v>
+        <v>29.36</v>
       </c>
       <c r="F33" t="n">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -1458,100 +1458,100 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C34" t="n">
-        <v>9657930100</v>
+        <v>9811363528</v>
       </c>
       <c r="D34" t="n">
-        <v>998</v>
+        <v>6503</v>
       </c>
       <c r="E34" t="n">
-        <v>4474.67</v>
+        <v>311.78</v>
       </c>
       <c r="F34" t="n">
-        <v>25139</v>
+        <v>1448</v>
       </c>
       <c r="G34" t="n">
-        <v>4430</v>
+        <v>433</v>
       </c>
       <c r="H34" t="n">
-        <v>12980</v>
+        <v>1268</v>
       </c>
       <c r="I34" t="n">
-        <v>310</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C35" t="n">
-        <v>9657930100</v>
+        <v>9630806627</v>
       </c>
       <c r="D35" t="n">
-        <v>998</v>
+        <v>1581</v>
       </c>
       <c r="E35" t="n">
-        <v>4474.67</v>
+        <v>358.77</v>
       </c>
       <c r="F35" t="n">
-        <v>25139</v>
+        <v>3446</v>
       </c>
       <c r="G35" t="n">
-        <v>4430</v>
+        <v>382</v>
       </c>
       <c r="H35" t="n">
-        <v>12980</v>
+        <v>1119</v>
       </c>
       <c r="I35" t="n">
-        <v>310</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>500635396</v>
       </c>
       <c r="C36" t="n">
-        <v>9773660250</v>
+        <v>9657930100</v>
       </c>
       <c r="D36" t="n">
-        <v>4514</v>
+        <v>5573</v>
       </c>
       <c r="E36" t="n">
-        <v>264.52</v>
+        <v>4474.67</v>
       </c>
       <c r="F36" t="n">
-        <v>2526</v>
+        <v>25139</v>
       </c>
       <c r="G36" t="n">
-        <v>96</v>
+        <v>4430</v>
       </c>
       <c r="H36" t="n">
-        <v>281</v>
+        <v>12980</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1582,125 +1582,125 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C38" t="n">
-        <v>9773660250</v>
+        <v>1841014603</v>
       </c>
       <c r="D38" t="n">
-        <v>4514</v>
+        <v>5267</v>
       </c>
       <c r="E38" t="n">
-        <v>264.52</v>
+        <v>38.14</v>
       </c>
       <c r="F38" t="n">
-        <v>2526</v>
+        <v>205</v>
       </c>
       <c r="G38" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="H38" t="n">
-        <v>281</v>
+        <v>106</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C39" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D39" t="n">
-        <v>6245</v>
+        <v>4177</v>
       </c>
       <c r="E39" t="n">
-        <v>30.55</v>
+        <v>358.77</v>
       </c>
       <c r="F39" t="n">
-        <v>265</v>
+        <v>3446</v>
       </c>
       <c r="G39" t="n">
-        <v>19</v>
+        <v>382</v>
       </c>
       <c r="H39" t="n">
-        <v>57</v>
+        <v>1119</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>500635396</v>
       </c>
       <c r="C40" t="n">
-        <v>9773660250</v>
+        <v>9657930100</v>
       </c>
       <c r="D40" t="n">
-        <v>4514</v>
+        <v>998</v>
       </c>
       <c r="E40" t="n">
-        <v>264.52</v>
+        <v>4474.67</v>
       </c>
       <c r="F40" t="n">
-        <v>2526</v>
+        <v>25139</v>
       </c>
       <c r="G40" t="n">
-        <v>96</v>
+        <v>4430</v>
       </c>
       <c r="H40" t="n">
-        <v>281</v>
+        <v>12980</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C41" t="n">
-        <v>2874903000</v>
+        <v>8878077181</v>
       </c>
       <c r="D41" t="n">
-        <v>6242</v>
+        <v>3989</v>
       </c>
       <c r="E41" t="n">
-        <v>28.63</v>
+        <v>539.88</v>
       </c>
       <c r="F41" t="n">
-        <v>228</v>
+        <v>1054</v>
       </c>
       <c r="G41" t="n">
-        <v>28</v>
+        <v>901</v>
       </c>
       <c r="H41" t="n">
-        <v>83</v>
+        <v>2640</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42">
@@ -1713,115 +1713,115 @@
         <v>63563817</v>
       </c>
       <c r="C42" t="n">
-        <v>1841014603</v>
+        <v>4190988310</v>
       </c>
       <c r="D42" t="n">
-        <v>2505</v>
+        <v>1583</v>
       </c>
       <c r="E42" t="n">
-        <v>38.14</v>
+        <v>29.36</v>
       </c>
       <c r="F42" t="n">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="G42" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H42" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C43" t="n">
-        <v>2874903000</v>
+        <v>9773660250</v>
       </c>
       <c r="D43" t="n">
-        <v>2574</v>
+        <v>4514</v>
       </c>
       <c r="E43" t="n">
-        <v>28.63</v>
+        <v>264.52</v>
       </c>
       <c r="F43" t="n">
-        <v>228</v>
+        <v>2526</v>
       </c>
       <c r="G43" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H43" t="n">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C44" t="n">
-        <v>9630806627</v>
+        <v>2874903000</v>
       </c>
       <c r="D44" t="n">
-        <v>6004</v>
+        <v>2596</v>
       </c>
       <c r="E44" t="n">
-        <v>358.77</v>
+        <v>28.63</v>
       </c>
       <c r="F44" t="n">
-        <v>3446</v>
+        <v>228</v>
       </c>
       <c r="G44" t="n">
-        <v>382</v>
+        <v>28</v>
       </c>
       <c r="H44" t="n">
-        <v>1119</v>
+        <v>83</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>63563817</v>
       </c>
       <c r="C45" t="n">
-        <v>4190988309</v>
+        <v>4190988310</v>
       </c>
       <c r="D45" t="n">
-        <v>2397</v>
+        <v>3180</v>
       </c>
       <c r="E45" t="n">
-        <v>30.55</v>
+        <v>29.36</v>
       </c>
       <c r="F45" t="n">
-        <v>265</v>
+        <v>118</v>
       </c>
       <c r="G45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -1834,158 +1834,158 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C46" t="n">
-        <v>9773660250</v>
+        <v>2874903000</v>
       </c>
       <c r="D46" t="n">
-        <v>4514</v>
+        <v>4667</v>
       </c>
       <c r="E46" t="n">
-        <v>264.52</v>
+        <v>28.63</v>
       </c>
       <c r="F46" t="n">
-        <v>2526</v>
+        <v>228</v>
       </c>
       <c r="G46" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="H46" t="n">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C47" t="n">
-        <v>9700005700</v>
+        <v>4190988309</v>
       </c>
       <c r="D47" t="n">
-        <v>5963</v>
+        <v>6082</v>
       </c>
       <c r="E47" t="n">
-        <v>17.63</v>
+        <v>30.55</v>
       </c>
       <c r="F47" t="n">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="G47" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H47" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C48" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D48" t="n">
-        <v>3304</v>
+        <v>6560</v>
       </c>
       <c r="E48" t="n">
-        <v>38.14</v>
+        <v>300.1</v>
       </c>
       <c r="F48" t="n">
-        <v>205</v>
+        <v>2619</v>
       </c>
       <c r="G48" t="n">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="H48" t="n">
-        <v>106</v>
+        <v>1173</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>63563817</v>
       </c>
       <c r="C49" t="n">
-        <v>4190988309</v>
+        <v>1841014603</v>
       </c>
       <c r="D49" t="n">
-        <v>3617</v>
+        <v>3304</v>
       </c>
       <c r="E49" t="n">
-        <v>30.55</v>
+        <v>38.14</v>
       </c>
       <c r="F49" t="n">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="G49" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H49" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>500635396</v>
       </c>
       <c r="C50" t="n">
-        <v>9657930100</v>
+        <v>9700005700</v>
       </c>
       <c r="D50" t="n">
-        <v>6133</v>
+        <v>5963</v>
       </c>
       <c r="E50" t="n">
-        <v>4474.67</v>
+        <v>17.63</v>
       </c>
       <c r="F50" t="n">
-        <v>25139</v>
+        <v>128</v>
       </c>
       <c r="G50" t="n">
-        <v>4430</v>
+        <v>30</v>
       </c>
       <c r="H50" t="n">
-        <v>12980</v>
+        <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>310</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1995,7 +1995,7 @@
         <v>2874903000</v>
       </c>
       <c r="D51" t="n">
-        <v>2574</v>
+        <v>1812</v>
       </c>
       <c r="E51" t="n">
         <v>28.63</v>
@@ -2016,559 +2016,559 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C52" t="n">
-        <v>9657930100</v>
+        <v>1841014603</v>
       </c>
       <c r="D52" t="n">
-        <v>5166</v>
+        <v>2889</v>
       </c>
       <c r="E52" t="n">
-        <v>4474.67</v>
+        <v>38.14</v>
       </c>
       <c r="F52" t="n">
-        <v>25139</v>
+        <v>205</v>
       </c>
       <c r="G52" t="n">
-        <v>4430</v>
+        <v>36</v>
       </c>
       <c r="H52" t="n">
-        <v>12980</v>
+        <v>106</v>
       </c>
       <c r="I52" t="n">
-        <v>310</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>63563817</v>
       </c>
       <c r="C53" t="n">
-        <v>4190988310</v>
+        <v>2874903000</v>
       </c>
       <c r="D53" t="n">
-        <v>3818</v>
+        <v>4738</v>
       </c>
       <c r="E53" t="n">
-        <v>29.36</v>
+        <v>28.63</v>
       </c>
       <c r="F53" t="n">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="G53" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H53" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C54" t="n">
-        <v>9811363528</v>
+        <v>4190988309</v>
       </c>
       <c r="D54" t="n">
-        <v>2288</v>
+        <v>4135</v>
       </c>
       <c r="E54" t="n">
-        <v>311.78</v>
+        <v>30.55</v>
       </c>
       <c r="F54" t="n">
-        <v>1448</v>
+        <v>265</v>
       </c>
       <c r="G54" t="n">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>1268</v>
+        <v>57</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C55" t="n">
-        <v>8878077181</v>
+        <v>4190988310</v>
       </c>
       <c r="D55" t="n">
-        <v>1048</v>
+        <v>6364</v>
       </c>
       <c r="E55" t="n">
-        <v>539.88</v>
+        <v>29.36</v>
       </c>
       <c r="F55" t="n">
-        <v>1054</v>
+        <v>118</v>
       </c>
       <c r="G55" t="n">
-        <v>901</v>
+        <v>18</v>
       </c>
       <c r="H55" t="n">
-        <v>2640</v>
+        <v>54</v>
       </c>
       <c r="I55" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C56" t="n">
-        <v>4190988310</v>
+        <v>9630806627</v>
       </c>
       <c r="D56" t="n">
-        <v>5840</v>
+        <v>2479</v>
       </c>
       <c r="E56" t="n">
-        <v>29.36</v>
+        <v>358.77</v>
       </c>
       <c r="F56" t="n">
-        <v>118</v>
+        <v>3446</v>
       </c>
       <c r="G56" t="n">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="H56" t="n">
-        <v>54</v>
+        <v>1119</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C57" t="n">
-        <v>4190988310</v>
+        <v>8878077181</v>
       </c>
       <c r="D57" t="n">
-        <v>3501</v>
+        <v>3989</v>
       </c>
       <c r="E57" t="n">
-        <v>29.36</v>
+        <v>539.88</v>
       </c>
       <c r="F57" t="n">
-        <v>118</v>
+        <v>1054</v>
       </c>
       <c r="G57" t="n">
-        <v>18</v>
+        <v>901</v>
       </c>
       <c r="H57" t="n">
-        <v>54</v>
+        <v>2640</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C58" t="n">
-        <v>2874903000</v>
+        <v>9628223555</v>
       </c>
       <c r="D58" t="n">
-        <v>2669</v>
+        <v>4165</v>
       </c>
       <c r="E58" t="n">
-        <v>28.63</v>
+        <v>300.1</v>
       </c>
       <c r="F58" t="n">
-        <v>228</v>
+        <v>2619</v>
       </c>
       <c r="G58" t="n">
+        <v>400</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1173</v>
+      </c>
+      <c r="I58" t="n">
         <v>28</v>
-      </c>
-      <c r="H58" t="n">
-        <v>83</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C59" t="n">
-        <v>9773660250</v>
+        <v>4190988309</v>
       </c>
       <c r="D59" t="n">
-        <v>4514</v>
+        <v>3617</v>
       </c>
       <c r="E59" t="n">
-        <v>264.52</v>
+        <v>30.55</v>
       </c>
       <c r="F59" t="n">
-        <v>2526</v>
+        <v>265</v>
       </c>
       <c r="G59" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="H59" t="n">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C60" t="n">
-        <v>4190988310</v>
+        <v>9773660250</v>
       </c>
       <c r="D60" t="n">
-        <v>4155</v>
+        <v>4514</v>
       </c>
       <c r="E60" t="n">
-        <v>29.36</v>
+        <v>264.52</v>
       </c>
       <c r="F60" t="n">
-        <v>118</v>
+        <v>2526</v>
       </c>
       <c r="G60" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H60" t="n">
-        <v>54</v>
+        <v>281</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>500635396</v>
       </c>
       <c r="C61" t="n">
-        <v>9700005700</v>
+        <v>9773660250</v>
       </c>
       <c r="D61" t="n">
-        <v>5453</v>
+        <v>4514</v>
       </c>
       <c r="E61" t="n">
-        <v>17.63</v>
+        <v>264.52</v>
       </c>
       <c r="F61" t="n">
-        <v>128</v>
+        <v>2526</v>
       </c>
       <c r="G61" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H61" t="n">
-        <v>88</v>
+        <v>281</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C62" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D62" t="n">
-        <v>6082</v>
+        <v>4706</v>
       </c>
       <c r="E62" t="n">
-        <v>30.55</v>
+        <v>311.78</v>
       </c>
       <c r="F62" t="n">
-        <v>265</v>
+        <v>1448</v>
       </c>
       <c r="G62" t="n">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="H62" t="n">
-        <v>57</v>
+        <v>1268</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C63" t="n">
-        <v>1841014603</v>
+        <v>9811363528</v>
       </c>
       <c r="D63" t="n">
-        <v>5267</v>
+        <v>669</v>
       </c>
       <c r="E63" t="n">
-        <v>38.14</v>
+        <v>311.78</v>
       </c>
       <c r="F63" t="n">
-        <v>205</v>
+        <v>1448</v>
       </c>
       <c r="G63" t="n">
-        <v>36</v>
+        <v>433</v>
       </c>
       <c r="H63" t="n">
-        <v>106</v>
+        <v>1268</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>63563817</v>
       </c>
       <c r="C64" t="n">
-        <v>1841014603</v>
+        <v>4190988310</v>
       </c>
       <c r="D64" t="n">
-        <v>3169</v>
+        <v>3501</v>
       </c>
       <c r="E64" t="n">
-        <v>38.14</v>
+        <v>29.36</v>
       </c>
       <c r="F64" t="n">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="G64" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H64" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C65" t="n">
-        <v>9811363528</v>
+        <v>9773660250</v>
       </c>
       <c r="D65" t="n">
-        <v>61</v>
+        <v>4514</v>
       </c>
       <c r="E65" t="n">
-        <v>311.78</v>
+        <v>264.52</v>
       </c>
       <c r="F65" t="n">
-        <v>1448</v>
+        <v>2526</v>
       </c>
       <c r="G65" t="n">
-        <v>433</v>
+        <v>96</v>
       </c>
       <c r="H65" t="n">
-        <v>1268</v>
+        <v>281</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C66" t="n">
-        <v>9773660250</v>
+        <v>9630806627</v>
       </c>
       <c r="D66" t="n">
-        <v>4514</v>
+        <v>3417</v>
       </c>
       <c r="E66" t="n">
-        <v>264.52</v>
+        <v>358.77</v>
       </c>
       <c r="F66" t="n">
-        <v>2526</v>
+        <v>3446</v>
       </c>
       <c r="G66" t="n">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="H66" t="n">
-        <v>281</v>
+        <v>1119</v>
       </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C67" t="n">
-        <v>9700005700</v>
+        <v>8878077181</v>
       </c>
       <c r="D67" t="n">
-        <v>5248</v>
+        <v>3989</v>
       </c>
       <c r="E67" t="n">
-        <v>17.63</v>
+        <v>539.88</v>
       </c>
       <c r="F67" t="n">
-        <v>128</v>
+        <v>1054</v>
       </c>
       <c r="G67" t="n">
-        <v>30</v>
+        <v>901</v>
       </c>
       <c r="H67" t="n">
-        <v>88</v>
+        <v>2640</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C68" t="n">
-        <v>9700005700</v>
+        <v>1841014603</v>
       </c>
       <c r="D68" t="n">
-        <v>5248</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>17.63</v>
+        <v>38.14</v>
       </c>
       <c r="F68" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="G68" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H68" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C69" t="n">
-        <v>4190988310</v>
+        <v>9628223555</v>
       </c>
       <c r="D69" t="n">
-        <v>6364</v>
+        <v>3353</v>
       </c>
       <c r="E69" t="n">
-        <v>29.36</v>
+        <v>300.1</v>
       </c>
       <c r="F69" t="n">
-        <v>118</v>
+        <v>2619</v>
       </c>
       <c r="G69" t="n">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="H69" t="n">
-        <v>54</v>
+        <v>1173</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
@@ -2578,28 +2578,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>525368335</v>
+        <v>63563817</v>
       </c>
       <c r="C70" t="n">
-        <v>9811363528</v>
+        <v>2874903000</v>
       </c>
       <c r="D70" t="n">
-        <v>3843</v>
+        <v>5241</v>
       </c>
       <c r="E70" t="n">
-        <v>311.78</v>
+        <v>28.63</v>
       </c>
       <c r="F70" t="n">
-        <v>1448</v>
+        <v>228</v>
       </c>
       <c r="G70" t="n">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="H70" t="n">
-        <v>1268</v>
+        <v>83</v>
       </c>
       <c r="I70" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2615,7 +2615,7 @@
         <v>2874903000</v>
       </c>
       <c r="D71" t="n">
-        <v>5995</v>
+        <v>1490</v>
       </c>
       <c r="E71" t="n">
         <v>28.63</v>
@@ -2636,156 +2636,156 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C72" t="n">
-        <v>9628223555</v>
+        <v>9700005700</v>
       </c>
       <c r="D72" t="n">
-        <v>734</v>
+        <v>6656</v>
       </c>
       <c r="E72" t="n">
-        <v>300.1</v>
+        <v>17.63</v>
       </c>
       <c r="F72" t="n">
-        <v>2619</v>
+        <v>128</v>
       </c>
       <c r="G72" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="H72" t="n">
-        <v>1173</v>
+        <v>88</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C73" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D73" t="n">
-        <v>6082</v>
+        <v>669</v>
       </c>
       <c r="E73" t="n">
-        <v>30.55</v>
+        <v>311.78</v>
       </c>
       <c r="F73" t="n">
-        <v>265</v>
+        <v>1448</v>
       </c>
       <c r="G73" t="n">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="H73" t="n">
-        <v>57</v>
+        <v>1268</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C74" t="n">
-        <v>9700005700</v>
+        <v>1841014603</v>
       </c>
       <c r="D74" t="n">
-        <v>5453</v>
+        <v>4713</v>
       </c>
       <c r="E74" t="n">
-        <v>17.63</v>
+        <v>38.14</v>
       </c>
       <c r="F74" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="G74" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H74" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C75" t="n">
-        <v>9628223555</v>
+        <v>9811363528</v>
       </c>
       <c r="D75" t="n">
-        <v>700</v>
+        <v>1131</v>
       </c>
       <c r="E75" t="n">
-        <v>300.1</v>
+        <v>311.78</v>
       </c>
       <c r="F75" t="n">
-        <v>2619</v>
+        <v>1448</v>
       </c>
       <c r="G75" t="n">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="H75" t="n">
-        <v>1173</v>
+        <v>1268</v>
       </c>
       <c r="I75" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C76" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D76" t="n">
-        <v>1048</v>
+        <v>1233</v>
       </c>
       <c r="E76" t="n">
-        <v>539.88</v>
+        <v>311.78</v>
       </c>
       <c r="F76" t="n">
-        <v>1054</v>
+        <v>1448</v>
       </c>
       <c r="G76" t="n">
-        <v>901</v>
+        <v>433</v>
       </c>
       <c r="H76" t="n">
-        <v>2640</v>
+        <v>1268</v>
       </c>
       <c r="I76" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77">
@@ -2795,28 +2795,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C77" t="n">
-        <v>9773660250</v>
+        <v>9630806627</v>
       </c>
       <c r="D77" t="n">
-        <v>4514</v>
+        <v>2203</v>
       </c>
       <c r="E77" t="n">
-        <v>264.52</v>
+        <v>358.77</v>
       </c>
       <c r="F77" t="n">
-        <v>2526</v>
+        <v>3446</v>
       </c>
       <c r="G77" t="n">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="H77" t="n">
-        <v>281</v>
+        <v>1119</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -2826,313 +2826,313 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C78" t="n">
-        <v>9630806627</v>
+        <v>4190988310</v>
       </c>
       <c r="D78" t="n">
-        <v>2501</v>
+        <v>2212</v>
       </c>
       <c r="E78" t="n">
-        <v>358.77</v>
+        <v>29.36</v>
       </c>
       <c r="F78" t="n">
-        <v>3446</v>
+        <v>118</v>
       </c>
       <c r="G78" t="n">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="H78" t="n">
-        <v>1119</v>
+        <v>54</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C79" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D79" t="n">
-        <v>3989</v>
+        <v>4514</v>
       </c>
       <c r="E79" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F79" t="n">
-        <v>1054</v>
+        <v>2526</v>
       </c>
       <c r="G79" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H79" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I79" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C80" t="n">
-        <v>9700005700</v>
+        <v>8878077181</v>
       </c>
       <c r="D80" t="n">
-        <v>5453</v>
+        <v>1048</v>
       </c>
       <c r="E80" t="n">
-        <v>17.63</v>
+        <v>539.88</v>
       </c>
       <c r="F80" t="n">
-        <v>128</v>
+        <v>1054</v>
       </c>
       <c r="G80" t="n">
-        <v>30</v>
+        <v>901</v>
       </c>
       <c r="H80" t="n">
-        <v>88</v>
+        <v>2640</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C81" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D81" t="n">
-        <v>4736</v>
+        <v>1048</v>
       </c>
       <c r="E81" t="n">
-        <v>311.78</v>
+        <v>539.88</v>
       </c>
       <c r="F81" t="n">
-        <v>1448</v>
+        <v>1054</v>
       </c>
       <c r="G81" t="n">
-        <v>433</v>
+        <v>901</v>
       </c>
       <c r="H81" t="n">
-        <v>1268</v>
+        <v>2640</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C82" t="n">
-        <v>8878077181</v>
+        <v>9628223555</v>
       </c>
       <c r="D82" t="n">
-        <v>3989</v>
+        <v>3769</v>
       </c>
       <c r="E82" t="n">
-        <v>539.88</v>
+        <v>300.1</v>
       </c>
       <c r="F82" t="n">
-        <v>1054</v>
+        <v>2619</v>
       </c>
       <c r="G82" t="n">
-        <v>901</v>
+        <v>400</v>
       </c>
       <c r="H82" t="n">
-        <v>2640</v>
+        <v>1173</v>
       </c>
       <c r="I82" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C83" t="n">
-        <v>9628223555</v>
+        <v>1841014603</v>
       </c>
       <c r="D83" t="n">
-        <v>3567</v>
+        <v>3304</v>
       </c>
       <c r="E83" t="n">
-        <v>300.1</v>
+        <v>38.14</v>
       </c>
       <c r="F83" t="n">
-        <v>2619</v>
+        <v>205</v>
       </c>
       <c r="G83" t="n">
-        <v>400</v>
+        <v>36</v>
       </c>
       <c r="H83" t="n">
-        <v>1173</v>
+        <v>106</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C84" t="n">
-        <v>4190988310</v>
+        <v>9628223555</v>
       </c>
       <c r="D84" t="n">
-        <v>2212</v>
+        <v>1094</v>
       </c>
       <c r="E84" t="n">
-        <v>29.36</v>
+        <v>300.1</v>
       </c>
       <c r="F84" t="n">
-        <v>118</v>
+        <v>2619</v>
       </c>
       <c r="G84" t="n">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="H84" t="n">
-        <v>54</v>
+        <v>1173</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C85" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D85" t="n">
-        <v>6538</v>
+        <v>5801</v>
       </c>
       <c r="E85" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F85" t="n">
-        <v>3446</v>
+        <v>205</v>
       </c>
       <c r="G85" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H85" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C86" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D86" t="n">
-        <v>1531</v>
+        <v>6157</v>
       </c>
       <c r="E86" t="n">
-        <v>300.1</v>
+        <v>358.77</v>
       </c>
       <c r="F86" t="n">
-        <v>2619</v>
+        <v>3446</v>
       </c>
       <c r="G86" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="H86" t="n">
-        <v>1173</v>
+        <v>1119</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>495817671</v>
+        <v>500635396</v>
       </c>
       <c r="C87" t="n">
-        <v>9630806627</v>
+        <v>9700005700</v>
       </c>
       <c r="D87" t="n">
-        <v>2195</v>
+        <v>5453</v>
       </c>
       <c r="E87" t="n">
-        <v>358.77</v>
+        <v>17.63</v>
       </c>
       <c r="F87" t="n">
-        <v>3446</v>
+        <v>128</v>
       </c>
       <c r="G87" t="n">
-        <v>382</v>
+        <v>30</v>
       </c>
       <c r="H87" t="n">
-        <v>1119</v>
+        <v>88</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3142,7 +3142,7 @@
         <v>4190988310</v>
       </c>
       <c r="D88" t="n">
-        <v>1583</v>
+        <v>1108</v>
       </c>
       <c r="E88" t="n">
         <v>29.36</v>
@@ -3163,63 +3163,63 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C89" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D89" t="n">
-        <v>5199</v>
+        <v>1048</v>
       </c>
       <c r="E89" t="n">
-        <v>358.77</v>
+        <v>539.88</v>
       </c>
       <c r="F89" t="n">
-        <v>3446</v>
+        <v>1054</v>
       </c>
       <c r="G89" t="n">
-        <v>382</v>
+        <v>901</v>
       </c>
       <c r="H89" t="n">
-        <v>1119</v>
+        <v>2640</v>
       </c>
       <c r="I89" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C90" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D90" t="n">
-        <v>1373</v>
+        <v>5027</v>
       </c>
       <c r="E90" t="n">
-        <v>300.1</v>
+        <v>358.77</v>
       </c>
       <c r="F90" t="n">
-        <v>2619</v>
+        <v>3446</v>
       </c>
       <c r="G90" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="H90" t="n">
-        <v>1173</v>
+        <v>1119</v>
       </c>
       <c r="I90" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/result3.xlsx
+++ b/results/excel/result3.xlsx
@@ -466,156 +466,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>500635396</v>
       </c>
       <c r="C2" t="n">
-        <v>9700005700</v>
+        <v>9657930100</v>
       </c>
       <c r="D2" t="n">
-        <v>4956</v>
+        <v>5874</v>
       </c>
       <c r="E2" t="n">
-        <v>17.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F2" t="n">
-        <v>128</v>
+        <v>25139</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>4430</v>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>12980</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C3" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D3" t="n">
-        <v>588</v>
+        <v>1853</v>
       </c>
       <c r="E3" t="n">
-        <v>311.78</v>
+        <v>358.77</v>
       </c>
       <c r="F3" t="n">
-        <v>1448</v>
+        <v>3446</v>
       </c>
       <c r="G3" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H3" t="n">
-        <v>1268</v>
+        <v>1119</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C4" t="n">
-        <v>9657930100</v>
+        <v>4190988310</v>
       </c>
       <c r="D4" t="n">
-        <v>998</v>
+        <v>1583</v>
       </c>
       <c r="E4" t="n">
-        <v>4474.67</v>
+        <v>29.36</v>
       </c>
       <c r="F4" t="n">
-        <v>25139</v>
+        <v>118</v>
       </c>
       <c r="G4" t="n">
-        <v>4430</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>12980</v>
+        <v>54</v>
       </c>
       <c r="I4" t="n">
-        <v>310</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C5" t="n">
-        <v>9657930100</v>
+        <v>4190988309</v>
       </c>
       <c r="D5" t="n">
-        <v>6452</v>
+        <v>6082</v>
       </c>
       <c r="E5" t="n">
-        <v>4474.67</v>
+        <v>30.55</v>
       </c>
       <c r="F5" t="n">
-        <v>25139</v>
+        <v>265</v>
       </c>
       <c r="G5" t="n">
-        <v>4430</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>12980</v>
+        <v>57</v>
       </c>
       <c r="I5" t="n">
-        <v>310</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C6" t="n">
-        <v>9700005700</v>
+        <v>9811363528</v>
       </c>
       <c r="D6" t="n">
-        <v>4956</v>
+        <v>6130</v>
       </c>
       <c r="E6" t="n">
-        <v>17.63</v>
+        <v>311.78</v>
       </c>
       <c r="F6" t="n">
-        <v>128</v>
+        <v>1448</v>
       </c>
       <c r="G6" t="n">
+        <v>433</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1268</v>
+      </c>
+      <c r="I6" t="n">
         <v>30</v>
-      </c>
-      <c r="H6" t="n">
-        <v>88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C7" t="n">
-        <v>4190988309</v>
+        <v>9630806627</v>
       </c>
       <c r="D7" t="n">
-        <v>3617</v>
+        <v>1754</v>
       </c>
       <c r="E7" t="n">
-        <v>30.55</v>
+        <v>358.77</v>
       </c>
       <c r="F7" t="n">
-        <v>265</v>
+        <v>3446</v>
       </c>
       <c r="G7" t="n">
-        <v>19</v>
+        <v>382</v>
       </c>
       <c r="H7" t="n">
-        <v>57</v>
+        <v>1119</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -656,96 +656,96 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C8" t="n">
-        <v>9628223555</v>
+        <v>9700005700</v>
       </c>
       <c r="D8" t="n">
-        <v>2551</v>
+        <v>6656</v>
       </c>
       <c r="E8" t="n">
-        <v>300.1</v>
+        <v>17.63</v>
       </c>
       <c r="F8" t="n">
-        <v>2619</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>1173</v>
+        <v>88</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C9" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D9" t="n">
-        <v>6082</v>
+        <v>1048</v>
       </c>
       <c r="E9" t="n">
-        <v>30.55</v>
+        <v>539.88</v>
       </c>
       <c r="F9" t="n">
-        <v>265</v>
+        <v>1054</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>901</v>
       </c>
       <c r="H9" t="n">
-        <v>57</v>
+        <v>2640</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C10" t="n">
-        <v>2874903000</v>
+        <v>9657930100</v>
       </c>
       <c r="D10" t="n">
-        <v>2596</v>
+        <v>6133</v>
       </c>
       <c r="E10" t="n">
-        <v>28.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F10" t="n">
-        <v>228</v>
+        <v>25139</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>4430</v>
       </c>
       <c r="H10" t="n">
-        <v>83</v>
+        <v>12980</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -755,7 +755,7 @@
         <v>8878077181</v>
       </c>
       <c r="D11" t="n">
-        <v>1048</v>
+        <v>3989</v>
       </c>
       <c r="E11" t="n">
         <v>539.88</v>
@@ -776,32 +776,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C12" t="n">
-        <v>9628223555</v>
+        <v>4190988309</v>
       </c>
       <c r="D12" t="n">
-        <v>5862</v>
+        <v>2397</v>
       </c>
       <c r="E12" t="n">
-        <v>300.1</v>
+        <v>30.55</v>
       </c>
       <c r="F12" t="n">
-        <v>2619</v>
+        <v>265</v>
       </c>
       <c r="G12" t="n">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>1173</v>
+        <v>57</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -814,186 +814,186 @@
         <v>63563817</v>
       </c>
       <c r="C13" t="n">
-        <v>4190988309</v>
+        <v>1841014603</v>
       </c>
       <c r="D13" t="n">
-        <v>6224</v>
+        <v>3169</v>
       </c>
       <c r="E13" t="n">
-        <v>30.55</v>
+        <v>38.14</v>
       </c>
       <c r="F13" t="n">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H13" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C14" t="n">
-        <v>2526158329</v>
+        <v>9628223555</v>
       </c>
       <c r="D14" t="n">
-        <v>934</v>
+        <v>5629</v>
       </c>
       <c r="E14" t="n">
-        <v>12.66</v>
+        <v>300.1</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>2619</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>1173</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C15" t="n">
-        <v>9630806627</v>
+        <v>8878077181</v>
       </c>
       <c r="D15" t="n">
-        <v>2125</v>
+        <v>1048</v>
       </c>
       <c r="E15" t="n">
-        <v>358.77</v>
+        <v>539.88</v>
       </c>
       <c r="F15" t="n">
-        <v>3446</v>
+        <v>1054</v>
       </c>
       <c r="G15" t="n">
-        <v>382</v>
+        <v>901</v>
       </c>
       <c r="H15" t="n">
-        <v>1119</v>
+        <v>2640</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C16" t="n">
-        <v>9657930100</v>
+        <v>9628223555</v>
       </c>
       <c r="D16" t="n">
-        <v>6133</v>
+        <v>3922</v>
       </c>
       <c r="E16" t="n">
-        <v>4474.67</v>
+        <v>300.1</v>
       </c>
       <c r="F16" t="n">
-        <v>25139</v>
+        <v>2619</v>
       </c>
       <c r="G16" t="n">
-        <v>4430</v>
+        <v>400</v>
       </c>
       <c r="H16" t="n">
-        <v>12980</v>
+        <v>1173</v>
       </c>
       <c r="I16" t="n">
-        <v>310</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C17" t="n">
-        <v>9773660250</v>
+        <v>9630806627</v>
       </c>
       <c r="D17" t="n">
-        <v>4514</v>
+        <v>2855</v>
       </c>
       <c r="E17" t="n">
-        <v>264.52</v>
+        <v>358.77</v>
       </c>
       <c r="F17" t="n">
-        <v>2526</v>
+        <v>3446</v>
       </c>
       <c r="G17" t="n">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="H17" t="n">
-        <v>281</v>
+        <v>1119</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C18" t="n">
-        <v>9628223555</v>
+        <v>4190988310</v>
       </c>
       <c r="D18" t="n">
-        <v>6017</v>
+        <v>4155</v>
       </c>
       <c r="E18" t="n">
-        <v>300.1</v>
+        <v>29.36</v>
       </c>
       <c r="F18" t="n">
-        <v>2619</v>
+        <v>118</v>
       </c>
       <c r="G18" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>1173</v>
+        <v>54</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1003,7 +1003,7 @@
         <v>9657930100</v>
       </c>
       <c r="D19" t="n">
-        <v>5573</v>
+        <v>998</v>
       </c>
       <c r="E19" t="n">
         <v>4474.67</v>
@@ -1024,63 +1024,63 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C20" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D20" t="n">
-        <v>6224</v>
+        <v>4255</v>
       </c>
       <c r="E20" t="n">
-        <v>30.55</v>
+        <v>311.78</v>
       </c>
       <c r="F20" t="n">
-        <v>265</v>
+        <v>1448</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="H20" t="n">
-        <v>57</v>
+        <v>1268</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C21" t="n">
-        <v>9700005700</v>
+        <v>9811363528</v>
       </c>
       <c r="D21" t="n">
-        <v>4956</v>
+        <v>3365</v>
       </c>
       <c r="E21" t="n">
-        <v>17.63</v>
+        <v>311.78</v>
       </c>
       <c r="F21" t="n">
-        <v>128</v>
+        <v>1448</v>
       </c>
       <c r="G21" t="n">
+        <v>433</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1268</v>
+      </c>
+      <c r="I21" t="n">
         <v>30</v>
-      </c>
-      <c r="H21" t="n">
-        <v>88</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1093,22 +1093,22 @@
         <v>63563817</v>
       </c>
       <c r="C22" t="n">
-        <v>4190988310</v>
+        <v>4190988309</v>
       </c>
       <c r="D22" t="n">
-        <v>2212</v>
+        <v>2397</v>
       </c>
       <c r="E22" t="n">
-        <v>29.36</v>
+        <v>30.55</v>
       </c>
       <c r="F22" t="n">
-        <v>118</v>
+        <v>265</v>
       </c>
       <c r="G22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1127,7 +1127,7 @@
         <v>9700005700</v>
       </c>
       <c r="D23" t="n">
-        <v>5453</v>
+        <v>1900</v>
       </c>
       <c r="E23" t="n">
         <v>17.63</v>
@@ -1148,280 +1148,280 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C24" t="n">
-        <v>9773660250</v>
+        <v>4190988310</v>
       </c>
       <c r="D24" t="n">
-        <v>4514</v>
+        <v>1583</v>
       </c>
       <c r="E24" t="n">
-        <v>264.52</v>
+        <v>29.36</v>
       </c>
       <c r="F24" t="n">
-        <v>2526</v>
+        <v>118</v>
       </c>
       <c r="G24" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>281</v>
+        <v>54</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C25" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D25" t="n">
-        <v>2890</v>
+        <v>1048</v>
       </c>
       <c r="E25" t="n">
-        <v>311.78</v>
+        <v>539.88</v>
       </c>
       <c r="F25" t="n">
-        <v>1448</v>
+        <v>1054</v>
       </c>
       <c r="G25" t="n">
-        <v>433</v>
+        <v>901</v>
       </c>
       <c r="H25" t="n">
-        <v>1268</v>
+        <v>2640</v>
       </c>
       <c r="I25" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C26" t="n">
-        <v>9773660250</v>
+        <v>9628223555</v>
       </c>
       <c r="D26" t="n">
-        <v>4514</v>
+        <v>3353</v>
       </c>
       <c r="E26" t="n">
-        <v>264.52</v>
+        <v>300.1</v>
       </c>
       <c r="F26" t="n">
-        <v>2526</v>
+        <v>2619</v>
       </c>
       <c r="G26" t="n">
-        <v>96</v>
+        <v>400</v>
       </c>
       <c r="H26" t="n">
-        <v>281</v>
+        <v>1173</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>500635396</v>
       </c>
       <c r="C27" t="n">
-        <v>9700005700</v>
+        <v>9773660250</v>
       </c>
       <c r="D27" t="n">
-        <v>5248</v>
+        <v>4514</v>
       </c>
       <c r="E27" t="n">
-        <v>17.63</v>
+        <v>264.52</v>
       </c>
       <c r="F27" t="n">
-        <v>128</v>
+        <v>2526</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H27" t="n">
-        <v>88</v>
+        <v>281</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C28" t="n">
-        <v>2874903000</v>
+        <v>9657930100</v>
       </c>
       <c r="D28" t="n">
-        <v>2959</v>
+        <v>5573</v>
       </c>
       <c r="E28" t="n">
-        <v>28.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F28" t="n">
-        <v>228</v>
+        <v>25139</v>
       </c>
       <c r="G28" t="n">
-        <v>28</v>
+        <v>4430</v>
       </c>
       <c r="H28" t="n">
-        <v>83</v>
+        <v>12980</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C29" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D29" t="n">
-        <v>1048</v>
+        <v>4514</v>
       </c>
       <c r="E29" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F29" t="n">
-        <v>1054</v>
+        <v>2526</v>
       </c>
       <c r="G29" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H29" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I29" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C30" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D30" t="n">
-        <v>2397</v>
+        <v>1048</v>
       </c>
       <c r="E30" t="n">
-        <v>30.55</v>
+        <v>539.88</v>
       </c>
       <c r="F30" t="n">
-        <v>265</v>
+        <v>1054</v>
       </c>
       <c r="G30" t="n">
-        <v>19</v>
+        <v>901</v>
       </c>
       <c r="H30" t="n">
-        <v>57</v>
+        <v>2640</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>63563817</v>
       </c>
       <c r="C31" t="n">
-        <v>1841014603</v>
+        <v>4190988310</v>
       </c>
       <c r="D31" t="n">
-        <v>6414</v>
+        <v>5812</v>
       </c>
       <c r="E31" t="n">
-        <v>38.14</v>
+        <v>29.36</v>
       </c>
       <c r="F31" t="n">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="G31" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H31" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C32" t="n">
-        <v>9657930100</v>
+        <v>4190988310</v>
       </c>
       <c r="D32" t="n">
-        <v>5166</v>
+        <v>228</v>
       </c>
       <c r="E32" t="n">
-        <v>4474.67</v>
+        <v>29.36</v>
       </c>
       <c r="F32" t="n">
-        <v>25139</v>
+        <v>118</v>
       </c>
       <c r="G32" t="n">
-        <v>4430</v>
+        <v>18</v>
       </c>
       <c r="H32" t="n">
-        <v>12980</v>
+        <v>54</v>
       </c>
       <c r="I32" t="n">
-        <v>310</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1434,124 +1434,124 @@
         <v>63563817</v>
       </c>
       <c r="C33" t="n">
-        <v>4190988310</v>
+        <v>2874903000</v>
       </c>
       <c r="D33" t="n">
-        <v>1108</v>
+        <v>2499</v>
       </c>
       <c r="E33" t="n">
-        <v>29.36</v>
+        <v>28.63</v>
       </c>
       <c r="F33" t="n">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="G33" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H33" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C34" t="n">
-        <v>9811363528</v>
+        <v>9700005700</v>
       </c>
       <c r="D34" t="n">
-        <v>6503</v>
+        <v>1900</v>
       </c>
       <c r="E34" t="n">
-        <v>311.78</v>
+        <v>17.63</v>
       </c>
       <c r="F34" t="n">
-        <v>1448</v>
+        <v>128</v>
       </c>
       <c r="G34" t="n">
-        <v>433</v>
+        <v>30</v>
       </c>
       <c r="H34" t="n">
-        <v>1268</v>
+        <v>88</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C35" t="n">
-        <v>9630806627</v>
+        <v>2874903000</v>
       </c>
       <c r="D35" t="n">
-        <v>1581</v>
+        <v>4798</v>
       </c>
       <c r="E35" t="n">
-        <v>358.77</v>
+        <v>28.63</v>
       </c>
       <c r="F35" t="n">
-        <v>3446</v>
+        <v>228</v>
       </c>
       <c r="G35" t="n">
-        <v>382</v>
+        <v>28</v>
       </c>
       <c r="H35" t="n">
-        <v>1119</v>
+        <v>83</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C36" t="n">
-        <v>9657930100</v>
+        <v>4190988310</v>
       </c>
       <c r="D36" t="n">
-        <v>5573</v>
+        <v>4713</v>
       </c>
       <c r="E36" t="n">
-        <v>4474.67</v>
+        <v>29.36</v>
       </c>
       <c r="F36" t="n">
-        <v>25139</v>
+        <v>118</v>
       </c>
       <c r="G36" t="n">
-        <v>4430</v>
+        <v>18</v>
       </c>
       <c r="H36" t="n">
-        <v>12980</v>
+        <v>54</v>
       </c>
       <c r="I36" t="n">
-        <v>310</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1561,7 +1561,7 @@
         <v>9657930100</v>
       </c>
       <c r="D37" t="n">
-        <v>998</v>
+        <v>5573</v>
       </c>
       <c r="E37" t="n">
         <v>4474.67</v>
@@ -1582,32 +1582,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C38" t="n">
-        <v>1841014603</v>
+        <v>9700005700</v>
       </c>
       <c r="D38" t="n">
-        <v>5267</v>
+        <v>6656</v>
       </c>
       <c r="E38" t="n">
-        <v>38.14</v>
+        <v>17.63</v>
       </c>
       <c r="F38" t="n">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="G38" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H38" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1617,34 +1617,34 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C39" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D39" t="n">
-        <v>4177</v>
+        <v>4675</v>
       </c>
       <c r="E39" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F39" t="n">
-        <v>3446</v>
+        <v>205</v>
       </c>
       <c r="G39" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H39" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1654,7 +1654,7 @@
         <v>9657930100</v>
       </c>
       <c r="D40" t="n">
-        <v>998</v>
+        <v>3587</v>
       </c>
       <c r="E40" t="n">
         <v>4474.67</v>
@@ -1675,38 +1675,38 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C41" t="n">
-        <v>8878077181</v>
+        <v>1841014603</v>
       </c>
       <c r="D41" t="n">
-        <v>3989</v>
+        <v>2123</v>
       </c>
       <c r="E41" t="n">
-        <v>539.88</v>
+        <v>38.14</v>
       </c>
       <c r="F41" t="n">
-        <v>1054</v>
+        <v>205</v>
       </c>
       <c r="G41" t="n">
-        <v>901</v>
+        <v>36</v>
       </c>
       <c r="H41" t="n">
-        <v>2640</v>
+        <v>106</v>
       </c>
       <c r="I41" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1716,7 +1716,7 @@
         <v>4190988310</v>
       </c>
       <c r="D42" t="n">
-        <v>1583</v>
+        <v>228</v>
       </c>
       <c r="E42" t="n">
         <v>29.36</v>
@@ -1737,218 +1737,218 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>500635396</v>
+        <v>525368335</v>
       </c>
       <c r="C43" t="n">
-        <v>9773660250</v>
+        <v>9811363528</v>
       </c>
       <c r="D43" t="n">
-        <v>4514</v>
+        <v>2572</v>
       </c>
       <c r="E43" t="n">
-        <v>264.52</v>
+        <v>311.78</v>
       </c>
       <c r="F43" t="n">
-        <v>2526</v>
+        <v>1448</v>
       </c>
       <c r="G43" t="n">
-        <v>96</v>
+        <v>433</v>
       </c>
       <c r="H43" t="n">
-        <v>281</v>
+        <v>1268</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C44" t="n">
-        <v>2874903000</v>
+        <v>9657930100</v>
       </c>
       <c r="D44" t="n">
-        <v>2596</v>
+        <v>3587</v>
       </c>
       <c r="E44" t="n">
-        <v>28.63</v>
+        <v>4474.67</v>
       </c>
       <c r="F44" t="n">
-        <v>228</v>
+        <v>25139</v>
       </c>
       <c r="G44" t="n">
-        <v>28</v>
+        <v>4430</v>
       </c>
       <c r="H44" t="n">
-        <v>83</v>
+        <v>12980</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>63563817</v>
       </c>
       <c r="C45" t="n">
-        <v>4190988310</v>
+        <v>2874903000</v>
       </c>
       <c r="D45" t="n">
-        <v>3180</v>
+        <v>4345</v>
       </c>
       <c r="E45" t="n">
-        <v>29.36</v>
+        <v>28.63</v>
       </c>
       <c r="F45" t="n">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="G45" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H45" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C46" t="n">
-        <v>2874903000</v>
+        <v>9773660250</v>
       </c>
       <c r="D46" t="n">
-        <v>4667</v>
+        <v>4514</v>
       </c>
       <c r="E46" t="n">
-        <v>28.63</v>
+        <v>264.52</v>
       </c>
       <c r="F46" t="n">
-        <v>228</v>
+        <v>2526</v>
       </c>
       <c r="G46" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H46" t="n">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C47" t="n">
-        <v>4190988309</v>
+        <v>9811363528</v>
       </c>
       <c r="D47" t="n">
-        <v>6082</v>
+        <v>2790</v>
       </c>
       <c r="E47" t="n">
-        <v>30.55</v>
+        <v>311.78</v>
       </c>
       <c r="F47" t="n">
-        <v>265</v>
+        <v>1448</v>
       </c>
       <c r="G47" t="n">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="H47" t="n">
-        <v>57</v>
+        <v>1268</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C48" t="n">
-        <v>9628223555</v>
+        <v>9657930100</v>
       </c>
       <c r="D48" t="n">
-        <v>6560</v>
+        <v>998</v>
       </c>
       <c r="E48" t="n">
-        <v>300.1</v>
+        <v>4474.67</v>
       </c>
       <c r="F48" t="n">
-        <v>2619</v>
+        <v>25139</v>
       </c>
       <c r="G48" t="n">
-        <v>400</v>
+        <v>4430</v>
       </c>
       <c r="H48" t="n">
-        <v>1173</v>
+        <v>12980</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C49" t="n">
-        <v>1841014603</v>
+        <v>9628223555</v>
       </c>
       <c r="D49" t="n">
-        <v>3304</v>
+        <v>2093</v>
       </c>
       <c r="E49" t="n">
-        <v>38.14</v>
+        <v>300.1</v>
       </c>
       <c r="F49" t="n">
-        <v>205</v>
+        <v>2619</v>
       </c>
       <c r="G49" t="n">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="H49" t="n">
-        <v>106</v>
+        <v>1173</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
@@ -1958,28 +1958,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>500635396</v>
+        <v>495817671</v>
       </c>
       <c r="C50" t="n">
-        <v>9700005700</v>
+        <v>9630806627</v>
       </c>
       <c r="D50" t="n">
-        <v>5963</v>
+        <v>308</v>
       </c>
       <c r="E50" t="n">
-        <v>17.63</v>
+        <v>358.77</v>
       </c>
       <c r="F50" t="n">
-        <v>128</v>
+        <v>3446</v>
       </c>
       <c r="G50" t="n">
-        <v>30</v>
+        <v>382</v>
       </c>
       <c r="H50" t="n">
-        <v>88</v>
+        <v>1119</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -1995,7 +1995,7 @@
         <v>2874903000</v>
       </c>
       <c r="D51" t="n">
-        <v>1812</v>
+        <v>2499</v>
       </c>
       <c r="E51" t="n">
         <v>28.63</v>
@@ -2016,94 +2016,94 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>63563817</v>
       </c>
       <c r="C52" t="n">
-        <v>1841014603</v>
+        <v>4190988309</v>
       </c>
       <c r="D52" t="n">
-        <v>2889</v>
+        <v>3617</v>
       </c>
       <c r="E52" t="n">
-        <v>38.14</v>
+        <v>30.55</v>
       </c>
       <c r="F52" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="G52" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H52" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>63563817</v>
       </c>
       <c r="C53" t="n">
-        <v>2874903000</v>
+        <v>4190988310</v>
       </c>
       <c r="D53" t="n">
-        <v>4738</v>
+        <v>4713</v>
       </c>
       <c r="E53" t="n">
-        <v>28.63</v>
+        <v>29.36</v>
       </c>
       <c r="F53" t="n">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="G53" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>63563817</v>
       </c>
       <c r="C54" t="n">
-        <v>4190988309</v>
+        <v>2874903000</v>
       </c>
       <c r="D54" t="n">
-        <v>4135</v>
+        <v>648</v>
       </c>
       <c r="E54" t="n">
-        <v>30.55</v>
+        <v>28.63</v>
       </c>
       <c r="F54" t="n">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="G54" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H54" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2116,186 +2116,186 @@
         <v>63563817</v>
       </c>
       <c r="C55" t="n">
-        <v>4190988310</v>
+        <v>2874903000</v>
       </c>
       <c r="D55" t="n">
-        <v>6364</v>
+        <v>1307</v>
       </c>
       <c r="E55" t="n">
-        <v>29.36</v>
+        <v>28.63</v>
       </c>
       <c r="F55" t="n">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="G55" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H55" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>495817671</v>
+        <v>495403620</v>
       </c>
       <c r="C56" t="n">
-        <v>9630806627</v>
+        <v>9628223555</v>
       </c>
       <c r="D56" t="n">
-        <v>2479</v>
+        <v>875</v>
       </c>
       <c r="E56" t="n">
-        <v>358.77</v>
+        <v>300.1</v>
       </c>
       <c r="F56" t="n">
-        <v>3446</v>
+        <v>2619</v>
       </c>
       <c r="G56" t="n">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="H56" t="n">
-        <v>1119</v>
+        <v>1173</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C57" t="n">
-        <v>8878077181</v>
+        <v>4190988309</v>
       </c>
       <c r="D57" t="n">
-        <v>3989</v>
+        <v>2706</v>
       </c>
       <c r="E57" t="n">
-        <v>539.88</v>
+        <v>30.55</v>
       </c>
       <c r="F57" t="n">
-        <v>1054</v>
+        <v>265</v>
       </c>
       <c r="G57" t="n">
-        <v>901</v>
+        <v>19</v>
       </c>
       <c r="H57" t="n">
-        <v>2640</v>
+        <v>57</v>
       </c>
       <c r="I57" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C58" t="n">
-        <v>9628223555</v>
+        <v>9700005700</v>
       </c>
       <c r="D58" t="n">
-        <v>4165</v>
+        <v>1900</v>
       </c>
       <c r="E58" t="n">
-        <v>300.1</v>
+        <v>17.63</v>
       </c>
       <c r="F58" t="n">
-        <v>2619</v>
+        <v>128</v>
       </c>
       <c r="G58" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="H58" t="n">
-        <v>1173</v>
+        <v>88</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C59" t="n">
-        <v>4190988309</v>
+        <v>8878077181</v>
       </c>
       <c r="D59" t="n">
-        <v>3617</v>
+        <v>3989</v>
       </c>
       <c r="E59" t="n">
-        <v>30.55</v>
+        <v>539.88</v>
       </c>
       <c r="F59" t="n">
-        <v>265</v>
+        <v>1054</v>
       </c>
       <c r="G59" t="n">
-        <v>19</v>
+        <v>901</v>
       </c>
       <c r="H59" t="n">
-        <v>57</v>
+        <v>2640</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>500635396</v>
       </c>
       <c r="C60" t="n">
-        <v>9773660250</v>
+        <v>9700005700</v>
       </c>
       <c r="D60" t="n">
-        <v>4514</v>
+        <v>5248</v>
       </c>
       <c r="E60" t="n">
-        <v>264.52</v>
+        <v>17.63</v>
       </c>
       <c r="F60" t="n">
-        <v>2526</v>
+        <v>128</v>
       </c>
       <c r="G60" t="n">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="H60" t="n">
-        <v>281</v>
+        <v>88</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2326,410 +2326,410 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C62" t="n">
-        <v>9811363528</v>
+        <v>9700005700</v>
       </c>
       <c r="D62" t="n">
-        <v>4706</v>
+        <v>4956</v>
       </c>
       <c r="E62" t="n">
-        <v>311.78</v>
+        <v>17.63</v>
       </c>
       <c r="F62" t="n">
-        <v>1448</v>
+        <v>128</v>
       </c>
       <c r="G62" t="n">
-        <v>433</v>
+        <v>30</v>
       </c>
       <c r="H62" t="n">
-        <v>1268</v>
+        <v>88</v>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>525368335</v>
+        <v>500635396</v>
       </c>
       <c r="C63" t="n">
-        <v>9811363528</v>
+        <v>9773660250</v>
       </c>
       <c r="D63" t="n">
-        <v>669</v>
+        <v>4514</v>
       </c>
       <c r="E63" t="n">
-        <v>311.78</v>
+        <v>264.52</v>
       </c>
       <c r="F63" t="n">
-        <v>1448</v>
+        <v>2526</v>
       </c>
       <c r="G63" t="n">
-        <v>433</v>
+        <v>96</v>
       </c>
       <c r="H63" t="n">
-        <v>1268</v>
+        <v>281</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C64" t="n">
-        <v>4190988310</v>
+        <v>9811363528</v>
       </c>
       <c r="D64" t="n">
-        <v>3501</v>
+        <v>5167</v>
       </c>
       <c r="E64" t="n">
-        <v>29.36</v>
+        <v>311.78</v>
       </c>
       <c r="F64" t="n">
-        <v>118</v>
+        <v>1448</v>
       </c>
       <c r="G64" t="n">
-        <v>18</v>
+        <v>433</v>
       </c>
       <c r="H64" t="n">
-        <v>54</v>
+        <v>1268</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C65" t="n">
-        <v>9773660250</v>
+        <v>2526158329</v>
       </c>
       <c r="D65" t="n">
-        <v>4514</v>
+        <v>1262</v>
       </c>
       <c r="E65" t="n">
-        <v>264.52</v>
+        <v>12.66</v>
       </c>
       <c r="F65" t="n">
-        <v>2526</v>
+        <v>37</v>
       </c>
       <c r="G65" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="H65" t="n">
-        <v>281</v>
+        <v>24</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C66" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D66" t="n">
-        <v>3417</v>
+        <v>4135</v>
       </c>
       <c r="E66" t="n">
-        <v>358.77</v>
+        <v>30.55</v>
       </c>
       <c r="F66" t="n">
-        <v>3446</v>
+        <v>265</v>
       </c>
       <c r="G66" t="n">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="H66" t="n">
-        <v>1119</v>
+        <v>57</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C67" t="n">
-        <v>8878077181</v>
+        <v>2874903000</v>
       </c>
       <c r="D67" t="n">
-        <v>3989</v>
+        <v>5351</v>
       </c>
       <c r="E67" t="n">
-        <v>539.88</v>
+        <v>28.63</v>
       </c>
       <c r="F67" t="n">
-        <v>1054</v>
+        <v>228</v>
       </c>
       <c r="G67" t="n">
-        <v>901</v>
+        <v>28</v>
       </c>
       <c r="H67" t="n">
-        <v>2640</v>
+        <v>83</v>
       </c>
       <c r="I67" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C68" t="n">
-        <v>1841014603</v>
+        <v>9773660250</v>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>4514</v>
       </c>
       <c r="E68" t="n">
-        <v>38.14</v>
+        <v>264.52</v>
       </c>
       <c r="F68" t="n">
-        <v>205</v>
+        <v>2526</v>
       </c>
       <c r="G68" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="H68" t="n">
-        <v>106</v>
+        <v>281</v>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>495403620</v>
+        <v>63563817</v>
       </c>
       <c r="C69" t="n">
-        <v>9628223555</v>
+        <v>2874903000</v>
       </c>
       <c r="D69" t="n">
-        <v>3353</v>
+        <v>2596</v>
       </c>
       <c r="E69" t="n">
-        <v>300.1</v>
+        <v>28.63</v>
       </c>
       <c r="F69" t="n">
-        <v>2619</v>
+        <v>228</v>
       </c>
       <c r="G69" t="n">
-        <v>400</v>
+        <v>28</v>
       </c>
       <c r="H69" t="n">
-        <v>1173</v>
+        <v>83</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>63563817</v>
+        <v>495817671</v>
       </c>
       <c r="C70" t="n">
-        <v>2874903000</v>
+        <v>9630806627</v>
       </c>
       <c r="D70" t="n">
-        <v>5241</v>
+        <v>2874</v>
       </c>
       <c r="E70" t="n">
-        <v>28.63</v>
+        <v>358.77</v>
       </c>
       <c r="F70" t="n">
-        <v>228</v>
+        <v>3446</v>
       </c>
       <c r="G70" t="n">
-        <v>28</v>
+        <v>382</v>
       </c>
       <c r="H70" t="n">
-        <v>83</v>
+        <v>1119</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>63563817</v>
+        <v>525368335</v>
       </c>
       <c r="C71" t="n">
-        <v>2874903000</v>
+        <v>9628223555</v>
       </c>
       <c r="D71" t="n">
-        <v>1490</v>
+        <v>2855</v>
       </c>
       <c r="E71" t="n">
-        <v>28.63</v>
+        <v>300.1</v>
       </c>
       <c r="F71" t="n">
-        <v>228</v>
+        <v>2619</v>
       </c>
       <c r="G71" t="n">
+        <v>400</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1173</v>
+      </c>
+      <c r="I71" t="n">
         <v>28</v>
-      </c>
-      <c r="H71" t="n">
-        <v>83</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>500635396</v>
+        <v>63563817</v>
       </c>
       <c r="C72" t="n">
-        <v>9700005700</v>
+        <v>1841014603</v>
       </c>
       <c r="D72" t="n">
-        <v>6656</v>
+        <v>6414</v>
       </c>
       <c r="E72" t="n">
-        <v>17.63</v>
+        <v>38.14</v>
       </c>
       <c r="F72" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="G72" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H72" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>525368335</v>
+        <v>495817671</v>
       </c>
       <c r="C73" t="n">
-        <v>9811363528</v>
+        <v>9630806627</v>
       </c>
       <c r="D73" t="n">
-        <v>669</v>
+        <v>3104</v>
       </c>
       <c r="E73" t="n">
-        <v>311.78</v>
+        <v>358.77</v>
       </c>
       <c r="F73" t="n">
-        <v>1448</v>
+        <v>3446</v>
       </c>
       <c r="G73" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="H73" t="n">
-        <v>1268</v>
+        <v>1119</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>63563817</v>
+        <v>500635396</v>
       </c>
       <c r="C74" t="n">
-        <v>1841014603</v>
+        <v>9700005700</v>
       </c>
       <c r="D74" t="n">
-        <v>4713</v>
+        <v>5248</v>
       </c>
       <c r="E74" t="n">
-        <v>38.14</v>
+        <v>17.63</v>
       </c>
       <c r="F74" t="n">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="G74" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H74" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2739,7 +2739,7 @@
         <v>9811363528</v>
       </c>
       <c r="D75" t="n">
-        <v>1131</v>
+        <v>4853</v>
       </c>
       <c r="E75" t="n">
         <v>311.78</v>
@@ -2760,63 +2760,63 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C76" t="n">
-        <v>9811363528</v>
+        <v>8878077181</v>
       </c>
       <c r="D76" t="n">
-        <v>1233</v>
+        <v>1048</v>
       </c>
       <c r="E76" t="n">
-        <v>311.78</v>
+        <v>539.88</v>
       </c>
       <c r="F76" t="n">
-        <v>1448</v>
+        <v>1054</v>
       </c>
       <c r="G76" t="n">
-        <v>433</v>
+        <v>901</v>
       </c>
       <c r="H76" t="n">
-        <v>1268</v>
+        <v>2640</v>
       </c>
       <c r="I76" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C77" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D77" t="n">
-        <v>2203</v>
+        <v>3304</v>
       </c>
       <c r="E77" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F77" t="n">
-        <v>3446</v>
+        <v>205</v>
       </c>
       <c r="G77" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H77" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2826,137 +2826,137 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>63563817</v>
+        <v>495403620</v>
       </c>
       <c r="C78" t="n">
-        <v>4190988310</v>
+        <v>9628223555</v>
       </c>
       <c r="D78" t="n">
-        <v>2212</v>
+        <v>5229</v>
       </c>
       <c r="E78" t="n">
-        <v>29.36</v>
+        <v>300.1</v>
       </c>
       <c r="F78" t="n">
-        <v>118</v>
+        <v>2619</v>
       </c>
       <c r="G78" t="n">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="H78" t="n">
-        <v>54</v>
+        <v>1173</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>500635396</v>
+        <v>495403620</v>
       </c>
       <c r="C79" t="n">
-        <v>9773660250</v>
+        <v>8878077181</v>
       </c>
       <c r="D79" t="n">
-        <v>4514</v>
+        <v>3989</v>
       </c>
       <c r="E79" t="n">
-        <v>264.52</v>
+        <v>539.88</v>
       </c>
       <c r="F79" t="n">
-        <v>2526</v>
+        <v>1054</v>
       </c>
       <c r="G79" t="n">
-        <v>96</v>
+        <v>901</v>
       </c>
       <c r="H79" t="n">
-        <v>281</v>
+        <v>2640</v>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>495403620</v>
+        <v>525368335</v>
       </c>
       <c r="C80" t="n">
-        <v>8878077181</v>
+        <v>9811363528</v>
       </c>
       <c r="D80" t="n">
-        <v>1048</v>
+        <v>317</v>
       </c>
       <c r="E80" t="n">
-        <v>539.88</v>
+        <v>311.78</v>
       </c>
       <c r="F80" t="n">
-        <v>1054</v>
+        <v>1448</v>
       </c>
       <c r="G80" t="n">
-        <v>901</v>
+        <v>433</v>
       </c>
       <c r="H80" t="n">
-        <v>2640</v>
+        <v>1268</v>
       </c>
       <c r="I80" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>495403620</v>
+        <v>500635396</v>
       </c>
       <c r="C81" t="n">
-        <v>8878077181</v>
+        <v>9773660250</v>
       </c>
       <c r="D81" t="n">
-        <v>1048</v>
+        <v>4514</v>
       </c>
       <c r="E81" t="n">
-        <v>539.88</v>
+        <v>264.52</v>
       </c>
       <c r="F81" t="n">
-        <v>1054</v>
+        <v>2526</v>
       </c>
       <c r="G81" t="n">
-        <v>901</v>
+        <v>96</v>
       </c>
       <c r="H81" t="n">
-        <v>2640</v>
+        <v>281</v>
       </c>
       <c r="I81" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>525368335</v>
+        <v>495403620</v>
       </c>
       <c r="C82" t="n">
         <v>9628223555</v>
       </c>
       <c r="D82" t="n">
-        <v>3769</v>
+        <v>703</v>
       </c>
       <c r="E82" t="n">
         <v>300.1</v>
@@ -2977,7 +2977,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2987,7 +2987,7 @@
         <v>1841014603</v>
       </c>
       <c r="D83" t="n">
-        <v>3304</v>
+        <v>4713</v>
       </c>
       <c r="E83" t="n">
         <v>38.14</v>
@@ -3008,94 +3008,94 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C84" t="n">
-        <v>9628223555</v>
+        <v>9630806627</v>
       </c>
       <c r="D84" t="n">
-        <v>1094</v>
+        <v>4843</v>
       </c>
       <c r="E84" t="n">
-        <v>300.1</v>
+        <v>358.77</v>
       </c>
       <c r="F84" t="n">
-        <v>2619</v>
+        <v>3446</v>
       </c>
       <c r="G84" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="H84" t="n">
-        <v>1173</v>
+        <v>1119</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>63563817</v>
       </c>
       <c r="C85" t="n">
-        <v>1841014603</v>
+        <v>4190988309</v>
       </c>
       <c r="D85" t="n">
-        <v>5801</v>
+        <v>4135</v>
       </c>
       <c r="E85" t="n">
-        <v>38.14</v>
+        <v>30.55</v>
       </c>
       <c r="F85" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="G85" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H85" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C86" t="n">
-        <v>9630806627</v>
+        <v>1841014603</v>
       </c>
       <c r="D86" t="n">
-        <v>6157</v>
+        <v>4675</v>
       </c>
       <c r="E86" t="n">
-        <v>358.77</v>
+        <v>38.14</v>
       </c>
       <c r="F86" t="n">
-        <v>3446</v>
+        <v>205</v>
       </c>
       <c r="G86" t="n">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>1119</v>
+        <v>106</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -3108,118 +3108,118 @@
         <v>500635396</v>
       </c>
       <c r="C87" t="n">
-        <v>9700005700</v>
+        <v>9773660250</v>
       </c>
       <c r="D87" t="n">
-        <v>5453</v>
+        <v>4514</v>
       </c>
       <c r="E87" t="n">
-        <v>17.63</v>
+        <v>264.52</v>
       </c>
       <c r="F87" t="n">
-        <v>128</v>
+        <v>2526</v>
       </c>
       <c r="G87" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H87" t="n">
-        <v>88</v>
+        <v>281</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>63563817</v>
       </c>
       <c r="C88" t="n">
-        <v>4190988310</v>
+        <v>1841014603</v>
       </c>
       <c r="D88" t="n">
-        <v>1108</v>
+        <v>4675</v>
       </c>
       <c r="E88" t="n">
-        <v>29.36</v>
+        <v>38.14</v>
       </c>
       <c r="F88" t="n">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="G88" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H88" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>495403620</v>
+        <v>495817671</v>
       </c>
       <c r="C89" t="n">
-        <v>8878077181</v>
+        <v>9630806627</v>
       </c>
       <c r="D89" t="n">
-        <v>1048</v>
+        <v>617</v>
       </c>
       <c r="E89" t="n">
-        <v>539.88</v>
+        <v>358.77</v>
       </c>
       <c r="F89" t="n">
-        <v>1054</v>
+        <v>3446</v>
       </c>
       <c r="G89" t="n">
-        <v>901</v>
+        <v>382</v>
       </c>
       <c r="H89" t="n">
-        <v>2640</v>
+        <v>1119</v>
       </c>
       <c r="I89" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>495817671</v>
+        <v>63563817</v>
       </c>
       <c r="C90" t="n">
-        <v>9630806627</v>
+        <v>4190988309</v>
       </c>
       <c r="D90" t="n">
-        <v>5027</v>
+        <v>6245</v>
       </c>
       <c r="E90" t="n">
-        <v>358.77</v>
+        <v>30.55</v>
       </c>
       <c r="F90" t="n">
-        <v>3446</v>
+        <v>265</v>
       </c>
       <c r="G90" t="n">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="H90" t="n">
-        <v>1119</v>
+        <v>57</v>
       </c>
       <c r="I90" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
